--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDF6758-3FF3-4FBA-9CB9-B72BD3E3C7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF22923-9AAA-46B9-8710-1E74D5A32BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF22923-9AAA-46B9-8710-1E74D5A32BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7267A00D-7179-4244-AF7C-0AB00F4B642E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31425" yWindow="2715" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{B96B48CA-B84A-43A1-8292-3F80D4ADBB67}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -35,7 +35,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">kun li:
@@ -46,7 +45,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>初始化奖池金额，精确到元
@@ -54,14 +52,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{96EF5400-4DAB-4141-970D-FF776268E4D3}">
+    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -70,7 +67,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -78,14 +74,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{33DF3B40-47F4-4886-9AE2-B5F72E9D226D}">
+    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -97,10 +92,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{6F32FEED-974A-492C-87D0-3A6A7B312DA8}">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text/>
     </comment>
-    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{B5CEF0F6-27CB-4392-993F-FDF6B1469C94}">
+    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -132,9 +127,15 @@
     <t>循环的假奖池上限倍率</t>
   </si>
   <si>
+    <t>真奖池奖金万分比</t>
+  </si>
+  <si>
     <t>循环的假奖池增长速率</t>
   </si>
   <si>
+    <t>中奖表现延迟时间</t>
+  </si>
+  <si>
     <t>奖池系数</t>
   </si>
   <si>
@@ -153,12 +154,39 @@
     <t>fakePoolMax</t>
   </si>
   <si>
+    <t>truePool</t>
+  </si>
+  <si>
     <t>growthRate</t>
   </si>
   <si>
     <t>poolProp</t>
   </si>
   <si>
+    <t>mini</t>
+  </si>
+  <si>
+    <t>10,500</t>
+  </si>
+  <si>
+    <t>minor</t>
+  </si>
+  <si>
+    <t>10,300</t>
+  </si>
+  <si>
+    <t>major</t>
+  </si>
+  <si>
+    <t>10,150</t>
+  </si>
+  <si>
+    <t>grand</t>
+  </si>
+  <si>
+    <t>10,50</t>
+  </si>
+  <si>
     <t>3连10%大奖</t>
   </si>
   <si>
@@ -171,42 +199,7 @@
     <t>5连50%大奖</t>
   </si>
   <si>
-    <t>真奖池奖金万分比</t>
-  </si>
-  <si>
-    <t>中奖表现延迟时间</t>
-  </si>
-  <si>
-    <t>truePool</t>
-  </si>
-  <si>
-    <t>DelayTime</t>
-  </si>
-  <si>
-    <t>mini</t>
-  </si>
-  <si>
-    <t>minor</t>
-  </si>
-  <si>
-    <t>major</t>
-  </si>
-  <si>
-    <t>grand</t>
-  </si>
-  <si>
-    <t>10,50</t>
-  </si>
-  <si>
-    <t>10,500</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,300</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,150</t>
+    <t>delayTime</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -215,10 +208,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,22 +224,43 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -257,34 +271,13 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -331,39 +324,40 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
@@ -432,13 +426,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -707,265 +694,265 @@
     <col min="3" max="3" width="18.75" customWidth="1"/>
     <col min="4" max="4" width="20.75" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="20.25" style="9" customWidth="1"/>
+    <col min="6" max="6" width="20.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
     <col min="8" max="8" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="A5" s="6">
         <v>100100101</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7">
         <v>10</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="8">
         <v>15</v>
       </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2000</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1700</v>
+      </c>
+      <c r="H5" s="6">
         <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>100100102</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="7">
         <v>20</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <v>25</v>
       </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="4">
-        <v>2000</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1700</v>
+      </c>
+      <c r="H6" s="6">
         <v>2500</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>100100103</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="7">
         <v>50</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="8">
         <v>60</v>
       </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="4">
-        <v>2000</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1700</v>
+      </c>
+      <c r="H7" s="6">
         <v>6000</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>100100104</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="7">
         <v>250</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="8">
         <v>300</v>
       </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="4">
-        <v>2000</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1700</v>
+      </c>
+      <c r="H8" s="6">
         <v>30000</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>101200101</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
         <v>1000</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="F9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
         <v>10</v>
       </c>
-      <c r="I9" s="7"/>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="A10" s="6">
         <v>101200102</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="B10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
         <v>3000</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="F10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
         <v>30</v>
       </c>
-      <c r="I10" s="7"/>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="A11" s="6">
         <v>101200103</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="B11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
         <v>5000</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
+      <c r="F11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
         <v>50</v>
       </c>
-      <c r="I11" s="7"/>
+      <c r="I11" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -1,33 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7267A00D-7179-4244-AF7C-0AB00F4B642E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31425" yWindow="2715" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
     <author>Administrator</author>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -74,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -92,17 +99,17 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="1">
       <text/>
     </comment>
-    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 玩家在奖池的累计贡献金额 =  玩家累计押注金额 * 押注抽水入奖池万分比 - 玩家累计获的此奖池奖金额
@@ -116,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>奖池ID</t>
   </si>
@@ -160,6 +167,9 @@
     <t>growthRate</t>
   </si>
   <si>
+    <t>delayTime</t>
+  </si>
+  <si>
     <t>poolProp</t>
   </si>
   <si>
@@ -187,31 +197,25 @@
     <t>10,50</t>
   </si>
   <si>
-    <t>3连10%大奖</t>
+    <t>5【夺宝】分散中50%大奖</t>
   </si>
   <si>
     <t>0,0</t>
-  </si>
-  <si>
-    <t>4连30%大奖</t>
-  </si>
-  <si>
-    <t>5连50%大奖</t>
-  </si>
-  <si>
-    <t>delayTime</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,11 +231,160 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -241,25 +394,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -267,24 +413,10 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,8 +429,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -321,13 +639,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -335,76 +893,84 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="百分比" xfId="1" builtinId="5"/>
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 2" xfId="50"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -420,9 +986,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -680,17 +1243,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="24.025" customWidth="1"/>
     <col min="3" max="3" width="18.75" customWidth="1"/>
     <col min="4" max="4" width="20.75" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
@@ -699,7 +1262,7 @@
     <col min="8" max="8" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -723,7 +1286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -746,7 +1309,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -762,216 +1325,159 @@
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>27</v>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>100100101</v>
-      </c>
-      <c r="B5" s="6" t="s">
+    <row r="5" ht="16.5" spans="1:8">
+      <c r="A5" s="7">
+        <v>4001001</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="8">
+        <v>10</v>
+      </c>
+      <c r="D5" s="9">
         <v>15</v>
       </c>
-      <c r="C5" s="7">
-        <v>10</v>
-      </c>
-      <c r="D5" s="8">
-        <v>15</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="7">
         <v>1700</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
-        <v>100100102</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7">
+    <row r="6" ht="16.5" spans="1:8">
+      <c r="A6" s="7">
+        <v>4001002</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8">
         <v>20</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <v>25</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <v>0</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="7">
         <v>1700</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
-        <v>100100103</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="7">
+    <row r="7" ht="16.5" spans="1:8">
+      <c r="A7" s="7">
+        <v>4001003</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="8">
         <v>50</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <v>60</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="F7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7">
         <v>1700</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>6000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
-        <v>100100104</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="7">
+    <row r="8" ht="16.5" spans="1:8">
+      <c r="A8" s="7">
+        <v>4001004</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="8">
         <v>250</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="9">
         <v>300</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>0</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="F8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="7">
         <v>1700</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>30000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
-        <v>101200101</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="7">
+    <row r="9" ht="16.5" spans="1:9">
+      <c r="A9" s="7">
+        <v>4014001</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="8">
         <v>0</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <v>0</v>
       </c>
-      <c r="E9" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="E9" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="7">
         <v>0</v>
       </c>
-      <c r="H9" s="6">
-        <v>10</v>
-      </c>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
-        <v>101200102</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3000</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
-        <v>30</v>
-      </c>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
-        <v>101200103</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
-        <v>5000</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
+      <c r="H9" s="7">
         <v>50</v>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I9" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8:B8">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B9">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10:B10">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11:B11">
+  <conditionalFormatting sqref="B9">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7267A00D-7179-4244-AF7C-0AB00F4B642E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A401FC-0360-4BC7-BDDA-099AED7CBD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31425" yWindow="2715" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30225" yWindow="2280" windowWidth="21600" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>奖池ID</t>
   </si>
@@ -160,6 +160,9 @@
     <t>growthRate</t>
   </si>
   <si>
+    <t>delayTime</t>
+  </si>
+  <si>
     <t>poolProp</t>
   </si>
   <si>
@@ -187,20 +190,10 @@
     <t>10,50</t>
   </si>
   <si>
-    <t>3连10%大奖</t>
+    <t>5【夺宝】分散中50%大奖</t>
   </si>
   <si>
     <t>0,0</t>
-  </si>
-  <si>
-    <t>4连30%大奖</t>
-  </si>
-  <si>
-    <t>5连50%大奖</t>
-  </si>
-  <si>
-    <t>delayTime</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -211,7 +204,7 @@
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,7 +229,24 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -247,23 +257,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
@@ -272,14 +265,6 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -322,14 +307,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -357,24 +343,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
     <cellStyle name="常规 73" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -686,11 +662,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="18.75" customWidth="1"/>
     <col min="4" max="4" width="20.75" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
@@ -762,11 +738,11 @@
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>27</v>
+      <c r="G3" t="s">
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
@@ -774,7 +750,7 @@
         <v>100100101</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="7">
         <v>10</v>
@@ -786,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="6">
         <v>1700</v>
@@ -800,7 +776,7 @@
         <v>100100102</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="7">
         <v>20</v>
@@ -812,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="6">
         <v>1700</v>
@@ -826,7 +802,7 @@
         <v>100100103</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7">
         <v>50</v>
@@ -838,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="6">
         <v>1700</v>
@@ -852,7 +828,7 @@
         <v>100100104</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7">
         <v>250</v>
@@ -864,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="6">
         <v>1700</v>
@@ -875,10 +851,10 @@
     </row>
     <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
-        <v>101200101</v>
+        <v>4014001</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="7">
         <v>0</v>
@@ -887,88 +863,31 @@
         <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" s="6">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
-        <v>101200102</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3000</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
-        <v>30</v>
-      </c>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
-        <v>101200103</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
-        <v>5000</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>50</v>
-      </c>
-      <c r="I11" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8:B8">
+  <conditionalFormatting sqref="A9">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B9">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="A1:B1 A5:B5 B6:B7 A6:A8">
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:B10">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11:B11">
+  <conditionalFormatting sqref="B9">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -1,33 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A401FC-0360-4BC7-BDDA-099AED7CBD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30225" yWindow="2280" windowWidth="21600" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
     <author>Administrator</author>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -74,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -92,17 +99,17 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="1">
       <text/>
     </comment>
-    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 玩家在奖池的累计贡献金额 =  玩家累计押注金额 * 押注抽水入奖池万分比 - 玩家累计获的此奖池奖金额
@@ -199,12 +206,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,23 +231,148 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -247,6 +383,24 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -258,18 +412,11 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,8 +429,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -306,81 +639,338 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="百分比" xfId="1" builtinId="5"/>
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 73" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 2" xfId="50"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -396,9 +986,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -656,17 +1243,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="2" max="2" width="24.025" customWidth="1"/>
     <col min="3" max="3" width="18.75" customWidth="1"/>
     <col min="4" max="4" width="20.75" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
@@ -675,7 +1262,7 @@
     <col min="8" max="8" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -699,7 +1286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -722,7 +1309,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -738,159 +1325,159 @@
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" ht="16.5" spans="1:8">
+      <c r="A5" s="7">
         <v>100100101</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <v>10</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="9">
         <v>15</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>1700</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" ht="16.5" spans="1:8">
+      <c r="A6" s="7">
         <v>100100102</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <v>20</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <v>25</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <v>0</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>1700</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" ht="16.5" spans="1:8">
+      <c r="A7" s="7">
         <v>100100103</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>50</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <v>60</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>1700</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>6000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" ht="16.5" spans="1:8">
+      <c r="A8" s="7">
         <v>100100104</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>250</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="9">
         <v>300</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>0</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>1700</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>30000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
-        <v>4014001</v>
-      </c>
-      <c r="B9" s="6" t="s">
+    <row r="9" ht="16.5" spans="1:9">
+      <c r="A9" s="7">
+        <v>101400101</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>0</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <v>0</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <v>5000</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>0</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <v>50</v>
       </c>
-      <c r="I9" s="10"/>
+      <c r="I9" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B5 B6:B7 A6:A8">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
     <t>奖池ID</t>
   </si>
@@ -197,10 +197,13 @@
     <t>10,50</t>
   </si>
   <si>
+    <t>财神-5个【财神】分散中50%大奖</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
     <t>5【夺宝】分散中50%大奖</t>
-  </si>
-  <si>
-    <t>0,0</t>
   </si>
 </sst>
 </file>
@@ -377,19 +380,19 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1249,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1436,45 +1439,188 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:9">
+    <row r="9" ht="16.5" spans="1:8">
       <c r="A9" s="7">
+        <v>100300101</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8">
+        <v>10</v>
+      </c>
+      <c r="D9" s="9">
+        <v>15</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:8">
+      <c r="A10" s="7">
+        <v>100300102</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8">
+        <v>20</v>
+      </c>
+      <c r="D10" s="9">
+        <v>25</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:8">
+      <c r="A11" s="7">
+        <v>100300103</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="8">
+        <v>50</v>
+      </c>
+      <c r="D11" s="9">
+        <v>60</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:8">
+      <c r="A12" s="7">
+        <v>100300104</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="8">
+        <v>250</v>
+      </c>
+      <c r="D12" s="9">
+        <v>300</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:9">
+      <c r="A13" s="7">
+        <v>101200101</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>50</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:9">
+      <c r="A14" s="7">
         <v>101400101</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="B14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
         <v>5000</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <v>50</v>
       </c>
-      <c r="I9" s="11"/>
+      <c r="I14" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -378,7 +378,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -391,35 +395,31 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,6 +429,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,7 +770,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -788,16 +794,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -806,91 +812,91 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -916,6 +922,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
@@ -1440,106 +1458,106 @@
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
-      <c r="A9" s="7">
+      <c r="A9" s="11">
         <v>100300101</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="12">
         <v>10</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="13">
         <v>15</v>
       </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
         <v>1500</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
-      <c r="A10" s="7">
+      <c r="A10" s="11">
         <v>100300102</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="12">
         <v>20</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="13">
         <v>25</v>
       </c>
-      <c r="E10" s="9">
-        <v>0</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
         <v>2500</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
-      <c r="A11" s="7">
+      <c r="A11" s="11">
         <v>100300103</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="12">
         <v>50</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="13">
         <v>60</v>
       </c>
-      <c r="E11" s="9">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10" t="s">
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
         <v>6000</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
-      <c r="A12" s="7">
+      <c r="A12" s="11">
         <v>100300104</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="12">
         <v>250</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="13">
         <v>300</v>
       </c>
-      <c r="E12" s="9">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
         <v>30000</v>
       </c>
     </row>
@@ -1568,7 +1586,7 @@
       <c r="H13" s="7">
         <v>50</v>
       </c>
-      <c r="I13" s="11"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="7">
@@ -1595,7 +1613,7 @@
       <c r="H14" s="7">
         <v>50</v>
       </c>
-      <c r="I14" s="11"/>
+      <c r="I14" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
   <si>
     <t>奖池ID</t>
   </si>
@@ -383,11 +383,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -397,12 +392,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
@@ -416,6 +405,17 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1615,29 +1615,139 @@
       </c>
       <c r="I14" s="15"/>
     </row>
+    <row r="15" ht="16.5" spans="1:8">
+      <c r="A15" s="7">
+        <v>102400101</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="8">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9">
+        <v>15</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:8">
+      <c r="A16" s="7">
+        <v>102400102</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8">
+        <v>20</v>
+      </c>
+      <c r="D16" s="9">
+        <v>25</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H16" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:8">
+      <c r="A17" s="7">
+        <v>102400103</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="8">
+        <v>50</v>
+      </c>
+      <c r="D17" s="9">
+        <v>60</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H17" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:8">
+      <c r="A18" s="7">
+        <v>102400104</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="8">
+        <v>250</v>
+      </c>
+      <c r="D18" s="9">
+        <v>300</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H18" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
   <si>
     <t>奖池ID</t>
   </si>
@@ -378,11 +378,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -392,7 +387,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -415,7 +415,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1283,7 +1283,7 @@
     <col min="8" max="8" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:8">
+    <row r="5" ht="16.5" spans="1:9">
       <c r="A5" s="7">
         <v>100100101</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:8">
+    <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="7">
         <v>100100102</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:8">
+    <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="7">
         <v>100100103</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:8">
+    <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="7">
         <v>100100104</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:8">
+    <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="11">
         <v>100300101</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:8">
+    <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="11">
         <v>100300102</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:8">
+    <row r="11" ht="16.5" spans="1:9">
       <c r="A11" s="11">
         <v>100300103</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:8">
+    <row r="12" ht="16.5" spans="1:9">
       <c r="A12" s="11">
         <v>100300104</v>
       </c>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="I14" s="15"/>
     </row>
-    <row r="15" ht="16.5" spans="1:8">
+    <row r="15" ht="16.5" spans="1:9">
       <c r="A15" s="7">
         <v>102400101</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:8">
+    <row r="16" ht="16.5" spans="1:9">
       <c r="A16" s="7">
         <v>102400102</v>
       </c>
@@ -1719,36 +1719,268 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="19" ht="16.5" spans="1:8">
+      <c r="A19" s="7">
+        <v>101700101</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="8">
+        <v>10</v>
+      </c>
+      <c r="D19" s="9">
+        <v>15</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:8">
+      <c r="A20" s="7">
+        <v>101700102</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8">
+        <v>20</v>
+      </c>
+      <c r="D20" s="9">
+        <v>25</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H20" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:8">
+      <c r="A21" s="7">
+        <v>101700103</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8">
+        <v>50</v>
+      </c>
+      <c r="D21" s="9">
+        <v>60</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H21" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:8">
+      <c r="A22" s="7">
+        <v>101700104</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="8">
+        <v>250</v>
+      </c>
+      <c r="D22" s="9">
+        <v>300</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H22" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:8">
+      <c r="A23" s="7">
+        <v>102200101</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="8">
+        <v>10</v>
+      </c>
+      <c r="D23" s="9">
+        <v>15</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H23" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:8">
+      <c r="A24" s="7">
+        <v>102200102</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8">
+        <v>20</v>
+      </c>
+      <c r="D24" s="9">
+        <v>25</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H24" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:8">
+      <c r="A25" s="7">
+        <v>102200103</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8">
+        <v>50</v>
+      </c>
+      <c r="D25" s="9">
+        <v>60</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H25" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:8">
+      <c r="A26" s="7">
+        <v>102200104</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="8">
+        <v>250</v>
+      </c>
+      <c r="D26" s="9">
+        <v>300</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H26" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="27">
   <si>
     <t>奖池ID</t>
   </si>
@@ -378,6 +378,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -385,17 +391,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -414,8 +409,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1927,60 +1927,176 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="27" ht="16.5" spans="1:8">
+      <c r="A27" s="7">
+        <v>102100101</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="8">
+        <v>10</v>
+      </c>
+      <c r="D27" s="9">
+        <v>15</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H27" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:8">
+      <c r="A28" s="7">
+        <v>102100102</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="8">
+        <v>20</v>
+      </c>
+      <c r="D28" s="9">
+        <v>25</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H28" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:8">
+      <c r="A29" s="7">
+        <v>102100103</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="8">
+        <v>50</v>
+      </c>
+      <c r="D29" s="9">
+        <v>60</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H29" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:8">
+      <c r="A30" s="7">
+        <v>102100104</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="8">
+        <v>250</v>
+      </c>
+      <c r="D30" s="9">
+        <v>300</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H30" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
     <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
+  <conditionalFormatting sqref="B22">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
+  <conditionalFormatting sqref="A26">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
+  <conditionalFormatting sqref="B26">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
+  <conditionalFormatting sqref="A30">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
+  <conditionalFormatting sqref="A27:A29">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
+  <conditionalFormatting sqref="B27:B29">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
   <si>
     <t>奖池ID</t>
   </si>
@@ -378,9 +378,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -403,13 +402,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1270,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2031,72 +2031,185 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="31" ht="16.5" spans="1:8">
+      <c r="A31" s="7">
+        <v>101800101</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="8">
+        <v>10</v>
+      </c>
+      <c r="D31" s="9">
+        <v>15</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H31" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:8">
+      <c r="A32" s="7">
+        <v>101800102</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="8">
+        <v>20</v>
+      </c>
+      <c r="D32" s="9">
+        <v>25</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H32" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:8">
+      <c r="A33" s="7">
+        <v>101800103</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="8">
+        <v>50</v>
+      </c>
+      <c r="D33" s="9">
+        <v>60</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H33" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:8">
+      <c r="A34" s="7">
+        <v>101800104</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="8">
+        <v>250</v>
+      </c>
+      <c r="D34" s="9">
+        <v>300</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H34" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
     <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="27">
   <si>
     <t>奖池ID</t>
   </si>
@@ -378,7 +378,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -390,32 +390,32 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2135,81 +2135,194 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="35" ht="16.5" spans="1:8">
+      <c r="A35" s="7">
+        <v>102500101</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="8">
+        <v>10</v>
+      </c>
+      <c r="D35" s="9">
+        <v>15</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H35" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:8">
+      <c r="A36" s="7">
+        <v>102500102</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="8">
+        <v>20</v>
+      </c>
+      <c r="D36" s="9">
+        <v>25</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H36" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:8">
+      <c r="A37" s="7">
+        <v>102500103</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="8">
+        <v>50</v>
+      </c>
+      <c r="D37" s="9">
+        <v>60</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H37" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:8">
+      <c r="A38" s="7">
+        <v>102500104</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="8">
+        <v>250</v>
+      </c>
+      <c r="D38" s="9">
+        <v>300</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H38" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
     <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="27">
   <si>
     <t>奖池ID</t>
   </si>
@@ -378,11 +378,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -390,6 +385,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -397,25 +404,18 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2239,90 +2239,203 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="39" ht="16.5" spans="1:8">
+      <c r="A39" s="7">
+        <v>102300101</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="8">
+        <v>10</v>
+      </c>
+      <c r="D39" s="9">
+        <v>15</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H39" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:8">
+      <c r="A40" s="7">
+        <v>102300102</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="8">
+        <v>20</v>
+      </c>
+      <c r="D40" s="9">
+        <v>25</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H40" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:8">
+      <c r="A41" s="7">
+        <v>102300103</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="8">
+        <v>50</v>
+      </c>
+      <c r="D41" s="9">
+        <v>60</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H41" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:8">
+      <c r="A42" s="7">
+        <v>102300104</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="8">
+        <v>250</v>
+      </c>
+      <c r="D42" s="9">
+        <v>300</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H42" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A42">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="28">
   <si>
     <t>奖池ID</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>5【夺宝】分散中50%大奖</t>
+  </si>
+  <si>
+    <t>触发全屏奖中50%大奖</t>
   </si>
 </sst>
 </file>
@@ -385,18 +388,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -409,13 +412,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2343,99 +2346,131 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="43" ht="16.5" spans="1:8">
+      <c r="A43" s="7">
+        <v>103400101</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="8">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="7">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
     <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A42">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
     <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A42">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
   <si>
     <t>奖池ID</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>5【夺宝】分散中50%大奖</t>
+  </si>
+  <si>
+    <t>触发全屏奖中50%大奖</t>
   </si>
 </sst>
 </file>
@@ -393,7 +396,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -409,13 +412,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2343,99 +2346,387 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="43" ht="16.5" spans="1:8">
+      <c r="A43" s="7">
+        <v>103400101</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="8">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="7">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:8">
+      <c r="A44" s="7">
+        <v>103500101</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="8">
+        <v>10</v>
+      </c>
+      <c r="D44" s="9">
+        <v>15</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H44" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:8">
+      <c r="A45" s="7">
+        <v>103500102</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="8">
+        <v>20</v>
+      </c>
+      <c r="D45" s="9">
+        <v>25</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H45" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:8">
+      <c r="A46" s="7">
+        <v>103500103</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="8">
+        <v>50</v>
+      </c>
+      <c r="D46" s="9">
+        <v>60</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H46" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:8">
+      <c r="A47" s="7">
+        <v>103500104</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="8">
+        <v>250</v>
+      </c>
+      <c r="D47" s="9">
+        <v>300</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H47" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:8">
+      <c r="A48" s="7">
+        <v>103501101</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="8">
+        <v>10</v>
+      </c>
+      <c r="D48" s="9">
+        <v>15</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H48" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:8">
+      <c r="A49" s="7">
+        <v>103501102</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="8">
+        <v>20</v>
+      </c>
+      <c r="D49" s="9">
+        <v>25</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H49" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:8">
+      <c r="A50" s="7">
+        <v>103501103</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="8">
+        <v>50</v>
+      </c>
+      <c r="D50" s="9">
+        <v>60</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H50" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:8">
+      <c r="A51" s="7">
+        <v>103501104</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="8">
+        <v>250</v>
+      </c>
+      <c r="D51" s="9">
+        <v>300</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H51" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A42">
     <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
     <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A42">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
   <si>
     <t>奖池ID</t>
   </si>
@@ -388,15 +388,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1273,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2372,105 +2372,361 @@
         <v>50</v>
       </c>
     </row>
+    <row r="44" ht="16.5" spans="1:8">
+      <c r="A44" s="7">
+        <v>103500101</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="8">
+        <v>10</v>
+      </c>
+      <c r="D44" s="9">
+        <v>15</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H44" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:8">
+      <c r="A45" s="7">
+        <v>103500102</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="8">
+        <v>20</v>
+      </c>
+      <c r="D45" s="9">
+        <v>25</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H45" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:8">
+      <c r="A46" s="7">
+        <v>103500103</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="8">
+        <v>50</v>
+      </c>
+      <c r="D46" s="9">
+        <v>60</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H46" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:8">
+      <c r="A47" s="7">
+        <v>103500104</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="8">
+        <v>250</v>
+      </c>
+      <c r="D47" s="9">
+        <v>300</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H47" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:8">
+      <c r="A48" s="7">
+        <v>103501101</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="8">
+        <v>10</v>
+      </c>
+      <c r="D48" s="9">
+        <v>15</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H48" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:8">
+      <c r="A49" s="7">
+        <v>103501102</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="8">
+        <v>20</v>
+      </c>
+      <c r="D49" s="9">
+        <v>25</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H49" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:8">
+      <c r="A50" s="7">
+        <v>103501103</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="8">
+        <v>50</v>
+      </c>
+      <c r="D50" s="9">
+        <v>60</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H50" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:8">
+      <c r="A51" s="7">
+        <v>103501104</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="8">
+        <v>250</v>
+      </c>
+      <c r="D51" s="9">
+        <v>300</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H51" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
     <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A42">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
     <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
+  <conditionalFormatting sqref="B39:B41">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A42">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -206,7 +206,10 @@
     <t>5【夺宝】分散中50%大奖</t>
   </si>
   <si>
-    <t>触发全屏奖中50%大奖</t>
+    <t>出发全屏奖中50%大奖</t>
+  </si>
+  <si>
+    <t>3【夺宝】分散中50%大奖</t>
   </si>
 </sst>
 </file>
@@ -388,15 +391,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -412,13 +415,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1273,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2580,153 +2583,143 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="52" ht="16.5" spans="1:8">
+      <c r="A52" s="7">
+        <v>103600101</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="8">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0</v>
+      </c>
+      <c r="E52" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="7">
+        <v>0</v>
+      </c>
+      <c r="H52" s="7">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A45">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A46">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A51">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:B46">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
     <cfRule type="duplicateValues" dxfId="0" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
+  <conditionalFormatting sqref="A9:B11">
     <cfRule type="duplicateValues" dxfId="0" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A42">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
   <si>
     <t>奖池ID</t>
   </si>
@@ -204,9 +204,6 @@
   </si>
   <si>
     <t>5【夺宝】分散中50%大奖</t>
-  </si>
-  <si>
-    <t>出发全屏奖中50%大奖</t>
   </si>
   <si>
     <t>3【夺宝】分散中50%大奖</t>
@@ -384,6 +381,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -391,9 +399,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -403,25 +411,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1276,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2351,261 +2348,235 @@
     </row>
     <row r="43" ht="16.5" spans="1:8">
       <c r="A43" s="7">
-        <v>103400101</v>
+        <v>103500101</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C43" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D43" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E43" s="9">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G43" s="7">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H43" s="7">
-        <v>50</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:8">
       <c r="A44" s="7">
-        <v>103500101</v>
+        <v>103500102</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C44" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D44" s="9">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E44" s="9">
         <v>0</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G44" s="7">
         <v>1700</v>
       </c>
       <c r="H44" s="7">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:8">
       <c r="A45" s="7">
-        <v>103500102</v>
+        <v>103500103</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C45" s="8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D45" s="9">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E45" s="9">
         <v>0</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G45" s="7">
         <v>1700</v>
       </c>
       <c r="H45" s="7">
-        <v>2500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:8">
       <c r="A46" s="7">
-        <v>103500103</v>
+        <v>103500104</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C46" s="8">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D46" s="9">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E46" s="9">
         <v>0</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G46" s="7">
         <v>1700</v>
       </c>
       <c r="H46" s="7">
-        <v>6000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:8">
       <c r="A47" s="7">
-        <v>103500104</v>
+        <v>103501101</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C47" s="8">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="D47" s="9">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="E47" s="9">
         <v>0</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G47" s="7">
         <v>1700</v>
       </c>
       <c r="H47" s="7">
-        <v>30000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:8">
       <c r="A48" s="7">
-        <v>103501101</v>
+        <v>103501102</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C48" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D48" s="9">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E48" s="9">
         <v>0</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G48" s="7">
         <v>1700</v>
       </c>
       <c r="H48" s="7">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:8">
       <c r="A49" s="7">
-        <v>103501102</v>
+        <v>103501103</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C49" s="8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D49" s="9">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E49" s="9">
         <v>0</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G49" s="7">
         <v>1700</v>
       </c>
       <c r="H49" s="7">
-        <v>2500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:8">
       <c r="A50" s="7">
-        <v>103501103</v>
+        <v>103501104</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C50" s="8">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D50" s="9">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E50" s="9">
         <v>0</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G50" s="7">
         <v>1700</v>
       </c>
       <c r="H50" s="7">
-        <v>6000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:8">
       <c r="A51" s="7">
-        <v>103501104</v>
+        <v>103600101</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C51" s="8">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D51" s="9">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E51" s="9">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G51" s="7">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:8">
-      <c r="A52" s="7">
-        <v>103600101</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="8">
-        <v>0</v>
-      </c>
-      <c r="D52" s="9">
-        <v>0</v>
-      </c>
-      <c r="E52" s="9">
-        <v>5000</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G52" s="7">
-        <v>0</v>
-      </c>
-      <c r="H52" s="7">
         <v>50</v>
       </c>
     </row>
@@ -2655,16 +2626,19 @@
   <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A21">
@@ -2682,7 +2656,7 @@
   <conditionalFormatting sqref="A35:A38">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A51">
+  <conditionalFormatting sqref="A39:A50">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:B21">
@@ -2703,13 +2677,10 @@
   <conditionalFormatting sqref="B39:B41">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B46">
+  <conditionalFormatting sqref="B43:B45">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48:B50">
+  <conditionalFormatting sqref="B47:B49">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="28">
   <si>
     <t>奖池ID</t>
   </si>
@@ -381,18 +381,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -405,20 +405,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1273,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2580,117 +2580,364 @@
         <v>50</v>
       </c>
     </row>
+    <row r="52" ht="16.5" spans="1:8">
+      <c r="A52" s="7">
+        <v>102800101</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="8">
+        <v>10</v>
+      </c>
+      <c r="D52" s="9">
+        <v>15</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H52" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:8">
+      <c r="A53" s="7">
+        <v>102800102</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="8">
+        <v>20</v>
+      </c>
+      <c r="D53" s="9">
+        <v>25</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H53" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:8">
+      <c r="A54" s="7">
+        <v>102800103</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="8">
+        <v>50</v>
+      </c>
+      <c r="D54" s="9">
+        <v>60</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H54" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:8">
+      <c r="A55" s="7">
+        <v>102800104</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="8">
+        <v>250</v>
+      </c>
+      <c r="D55" s="9">
+        <v>300</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H55" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:8">
+      <c r="A56" s="7">
+        <v>102000101</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="8">
+        <v>10</v>
+      </c>
+      <c r="D56" s="9">
+        <v>15</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H56" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:8">
+      <c r="A57" s="7">
+        <v>102000102</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="8">
+        <v>20</v>
+      </c>
+      <c r="D57" s="9">
+        <v>25</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H57" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:8">
+      <c r="A58" s="7">
+        <v>102000103</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="8">
+        <v>50</v>
+      </c>
+      <c r="D58" s="9">
+        <v>60</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H58" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:8">
+      <c r="A59" s="7">
+        <v>102000104</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="8">
+        <v>250</v>
+      </c>
+      <c r="D59" s="9">
+        <v>300</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H59" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="0" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A50">
     <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="A56:A59">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:B45">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B49">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A50">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B45">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B49">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="28">
   <si>
     <t>奖池ID</t>
   </si>
@@ -381,11 +381,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -406,8 +401,12 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -418,7 +417,8 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1273,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2788,156 +2788,275 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="60" ht="16.5" spans="1:8">
+      <c r="A60" s="7">
+        <v>103800101</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="8">
+        <v>10</v>
+      </c>
+      <c r="D60" s="9">
+        <v>15</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H60" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:8">
+      <c r="A61" s="7">
+        <v>103800102</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="8">
+        <v>20</v>
+      </c>
+      <c r="D61" s="9">
+        <v>25</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H61" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:8">
+      <c r="A62" s="7">
+        <v>103800103</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="8">
+        <v>50</v>
+      </c>
+      <c r="D62" s="9">
+        <v>60</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H62" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:8">
+      <c r="A63" s="7">
+        <v>103800104</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="8">
+        <v>250</v>
+      </c>
+      <c r="D63" s="9">
+        <v>300</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H63" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="0" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A50">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56:A59">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60:A63">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:B45">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B49">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A50">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56:A59">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B45">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B49">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>5【夺宝】分散中50%大奖</t>
+  </si>
+  <si>
+    <t>全屏奖中50%大奖</t>
   </si>
   <si>
     <t>3【夺宝】分散中50%大奖</t>
@@ -381,18 +384,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -405,14 +403,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1273,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2348,235 +2351,261 @@
     </row>
     <row r="43" ht="16.5" spans="1:8">
       <c r="A43" s="7">
-        <v>103500101</v>
+        <v>103400101</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C43" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D43" s="9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E43" s="9">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G43" s="7">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>1500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:8">
       <c r="A44" s="7">
-        <v>103500102</v>
+        <v>103500101</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C44" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D44" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E44" s="9">
         <v>0</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G44" s="7">
         <v>1700</v>
       </c>
       <c r="H44" s="7">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:8">
       <c r="A45" s="7">
-        <v>103500103</v>
+        <v>103500102</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="8">
         <v>20</v>
       </c>
-      <c r="C45" s="8">
-        <v>50</v>
-      </c>
       <c r="D45" s="9">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E45" s="9">
         <v>0</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G45" s="7">
         <v>1700</v>
       </c>
       <c r="H45" s="7">
-        <v>6000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:8">
       <c r="A46" s="7">
-        <v>103500104</v>
+        <v>103500103</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C46" s="8">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="D46" s="9">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E46" s="9">
         <v>0</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G46" s="7">
         <v>1700</v>
       </c>
       <c r="H46" s="7">
-        <v>30000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:8">
       <c r="A47" s="7">
-        <v>103501101</v>
+        <v>103500104</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C47" s="8">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="D47" s="9">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E47" s="9">
         <v>0</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G47" s="7">
         <v>1700</v>
       </c>
       <c r="H47" s="7">
-        <v>1500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:8">
       <c r="A48" s="7">
-        <v>103501102</v>
+        <v>103501101</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C48" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D48" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E48" s="9">
         <v>0</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G48" s="7">
         <v>1700</v>
       </c>
       <c r="H48" s="7">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:8">
       <c r="A49" s="7">
-        <v>103501103</v>
+        <v>103501102</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="8">
         <v>20</v>
       </c>
-      <c r="C49" s="8">
-        <v>50</v>
-      </c>
       <c r="D49" s="9">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E49" s="9">
         <v>0</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G49" s="7">
         <v>1700</v>
       </c>
       <c r="H49" s="7">
-        <v>6000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:8">
       <c r="A50" s="7">
-        <v>103501104</v>
+        <v>103501103</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C50" s="8">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="D50" s="9">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E50" s="9">
         <v>0</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G50" s="7">
         <v>1700</v>
       </c>
       <c r="H50" s="7">
-        <v>30000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:8">
       <c r="A51" s="7">
+        <v>103501104</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="8">
+        <v>250</v>
+      </c>
+      <c r="D51" s="9">
+        <v>300</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H51" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:8">
+      <c r="A52" s="7">
         <v>103600101</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="8">
-        <v>0</v>
-      </c>
-      <c r="D51" s="9">
-        <v>0</v>
-      </c>
-      <c r="E51" s="9">
+      <c r="B52" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="8">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0</v>
+      </c>
+      <c r="E52" s="9">
         <v>5000</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F52" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G51" s="7">
-        <v>0</v>
-      </c>
-      <c r="H51" s="7">
+      <c r="G52" s="7">
+        <v>0</v>
+      </c>
+      <c r="H52" s="7">
         <v>50</v>
       </c>
     </row>
@@ -2626,19 +2655,16 @@
   <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B47">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
+  <conditionalFormatting sqref="A52">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A21">
@@ -2656,7 +2682,7 @@
   <conditionalFormatting sqref="A35:A38">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A50">
+  <conditionalFormatting sqref="A39:A51">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:B21">
@@ -2677,10 +2703,13 @@
   <conditionalFormatting sqref="B39:B41">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B45">
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:B46">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B49">
+  <conditionalFormatting sqref="B48:B50">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -206,7 +206,7 @@
     <t>5【夺宝】分散中50%大奖</t>
   </si>
   <si>
-    <t>全屏奖中50%大奖</t>
+    <t>全屏奖50%触发大奖</t>
   </si>
   <si>
     <t>3【夺宝】分散中50%大奖</t>
@@ -384,9 +384,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -400,22 +416,6 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2377,349 +2377,744 @@
     </row>
     <row r="44" ht="16.5" spans="1:8">
       <c r="A44" s="7">
-        <v>103500101</v>
+        <v>103401101</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C44" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D44" s="9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E44" s="9">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G44" s="7">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7">
-        <v>1500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:8">
       <c r="A45" s="7">
-        <v>103500102</v>
+        <v>103500101</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C45" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D45" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E45" s="9">
         <v>0</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G45" s="7">
         <v>1700</v>
       </c>
       <c r="H45" s="7">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:8">
       <c r="A46" s="7">
-        <v>103500103</v>
+        <v>103500102</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="8">
         <v>20</v>
       </c>
-      <c r="C46" s="8">
-        <v>50</v>
-      </c>
       <c r="D46" s="9">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E46" s="9">
         <v>0</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G46" s="7">
         <v>1700</v>
       </c>
       <c r="H46" s="7">
-        <v>6000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:8">
       <c r="A47" s="7">
-        <v>103500104</v>
+        <v>103500103</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C47" s="8">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="D47" s="9">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E47" s="9">
         <v>0</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G47" s="7">
         <v>1700</v>
       </c>
       <c r="H47" s="7">
-        <v>30000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:8">
       <c r="A48" s="7">
-        <v>103501101</v>
+        <v>103500104</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C48" s="8">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="D48" s="9">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E48" s="9">
         <v>0</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G48" s="7">
         <v>1700</v>
       </c>
       <c r="H48" s="7">
-        <v>1500</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:8">
       <c r="A49" s="7">
-        <v>103501102</v>
+        <v>103501101</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C49" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D49" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E49" s="9">
         <v>0</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G49" s="7">
         <v>1700</v>
       </c>
       <c r="H49" s="7">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:8">
       <c r="A50" s="7">
-        <v>103501103</v>
+        <v>103501102</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="8">
         <v>20</v>
       </c>
-      <c r="C50" s="8">
-        <v>50</v>
-      </c>
       <c r="D50" s="9">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E50" s="9">
         <v>0</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G50" s="7">
         <v>1700</v>
       </c>
       <c r="H50" s="7">
-        <v>6000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:8">
       <c r="A51" s="7">
-        <v>103501104</v>
+        <v>103501103</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C51" s="8">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="D51" s="9">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E51" s="9">
         <v>0</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G51" s="7">
         <v>1700</v>
       </c>
       <c r="H51" s="7">
-        <v>30000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:8">
       <c r="A52" s="7">
+        <v>103501104</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="8">
+        <v>250</v>
+      </c>
+      <c r="D52" s="9">
+        <v>300</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H52" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:8">
+      <c r="A53" s="7">
         <v>103600101</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B53" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="8">
-        <v>0</v>
-      </c>
-      <c r="D52" s="9">
-        <v>0</v>
-      </c>
-      <c r="E52" s="9">
+      <c r="C53" s="8">
+        <v>0</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9">
         <v>5000</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F53" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G52" s="7">
-        <v>0</v>
-      </c>
-      <c r="H52" s="7">
+      <c r="G53" s="7">
+        <v>0</v>
+      </c>
+      <c r="H53" s="7">
         <v>50</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:8">
+      <c r="A54" s="7">
+        <v>102800101</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="8">
+        <v>10</v>
+      </c>
+      <c r="D54" s="9">
+        <v>15</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H54" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:8">
+      <c r="A55" s="7">
+        <v>102800102</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="8">
+        <v>20</v>
+      </c>
+      <c r="D55" s="9">
+        <v>25</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H55" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:8">
+      <c r="A56" s="7">
+        <v>102800103</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="8">
+        <v>50</v>
+      </c>
+      <c r="D56" s="9">
+        <v>60</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H56" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:8">
+      <c r="A57" s="7">
+        <v>102800104</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="8">
+        <v>250</v>
+      </c>
+      <c r="D57" s="9">
+        <v>300</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H57" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:8">
+      <c r="A58" s="7">
+        <v>102000101</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="8">
+        <v>10</v>
+      </c>
+      <c r="D58" s="9">
+        <v>15</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H58" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:8">
+      <c r="A59" s="7">
+        <v>102000102</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="8">
+        <v>20</v>
+      </c>
+      <c r="D59" s="9">
+        <v>25</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H59" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:8">
+      <c r="A60" s="7">
+        <v>102000103</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="8">
+        <v>50</v>
+      </c>
+      <c r="D60" s="9">
+        <v>60</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H60" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:8">
+      <c r="A61" s="7">
+        <v>102000104</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="8">
+        <v>250</v>
+      </c>
+      <c r="D61" s="9">
+        <v>300</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H61" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:8">
+      <c r="A62" s="7">
+        <v>103800101</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="8">
+        <v>10</v>
+      </c>
+      <c r="D62" s="9">
+        <v>15</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H62" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:8">
+      <c r="A63" s="7">
+        <v>103800102</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="8">
+        <v>20</v>
+      </c>
+      <c r="D63" s="9">
+        <v>25</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H63" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:8">
+      <c r="A64" s="7">
+        <v>103800103</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="8">
+        <v>50</v>
+      </c>
+      <c r="D64" s="9">
+        <v>60</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H64" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:8">
+      <c r="A65" s="7">
+        <v>103800104</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="8">
+        <v>250</v>
+      </c>
+      <c r="D65" s="9">
+        <v>300</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H65" s="7">
+        <v>30000</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
     <cfRule type="duplicateValues" dxfId="0" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
     <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A51">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B46">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48:B50">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -389,6 +389,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -396,12 +401,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -413,9 +413,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2947,174 +2947,293 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="66" ht="16.5" spans="1:8">
+      <c r="A66" s="7">
+        <v>102700101</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="8">
+        <v>10</v>
+      </c>
+      <c r="D66" s="9">
+        <v>15</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H66" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:8">
+      <c r="A67" s="7">
+        <v>102700102</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="8">
+        <v>20</v>
+      </c>
+      <c r="D67" s="9">
+        <v>25</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H67" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:8">
+      <c r="A68" s="7">
+        <v>102700103</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="8">
+        <v>50</v>
+      </c>
+      <c r="D68" s="9">
+        <v>60</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H68" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:8">
+      <c r="A69" s="7">
+        <v>102700104</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="8">
+        <v>250</v>
+      </c>
+      <c r="D69" s="9">
+        <v>300</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H69" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="0" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:A61">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A65">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -384,16 +384,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -401,8 +391,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -416,6 +405,17 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -3051,189 +3051,340 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="70" ht="16.5" spans="1:8">
+      <c r="A70" s="7">
+        <v>103700101</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="8">
+        <v>0</v>
+      </c>
+      <c r="D70" s="9">
+        <v>0</v>
+      </c>
+      <c r="E70" s="9">
+        <v>5000</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" s="7">
+        <v>0</v>
+      </c>
+      <c r="H70" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:8">
+      <c r="A71" s="7">
+        <v>103100101</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="8">
+        <v>10</v>
+      </c>
+      <c r="D71" s="9">
+        <v>15</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H71" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:8">
+      <c r="A72" s="7">
+        <v>103100102</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="8">
+        <v>20</v>
+      </c>
+      <c r="D72" s="9">
+        <v>25</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H72" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:8">
+      <c r="A73" s="7">
+        <v>103100103</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="8">
+        <v>50</v>
+      </c>
+      <c r="D73" s="9">
+        <v>60</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H73" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:8">
+      <c r="A74" s="7">
+        <v>103100104</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="8">
+        <v>250</v>
+      </c>
+      <c r="D74" s="9">
+        <v>300</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H74" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
     <cfRule type="duplicateValues" dxfId="0" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
     <cfRule type="duplicateValues" dxfId="0" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71:A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:A61">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A65">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66:A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -391,7 +391,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -403,19 +404,18 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -3181,210 +3181,448 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="75" ht="16.5" spans="1:8">
+      <c r="A75" s="7">
+        <v>104000101</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="8">
+        <v>10</v>
+      </c>
+      <c r="D75" s="9">
+        <v>15</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H75" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:8">
+      <c r="A76" s="7">
+        <v>104000102</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="8">
+        <v>20</v>
+      </c>
+      <c r="D76" s="9">
+        <v>25</v>
+      </c>
+      <c r="E76" s="9">
+        <v>0</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H76" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:8">
+      <c r="A77" s="7">
+        <v>104000103</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="8">
+        <v>50</v>
+      </c>
+      <c r="D77" s="9">
+        <v>60</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H77" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:8">
+      <c r="A78" s="7">
+        <v>104000104</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="8">
+        <v>250</v>
+      </c>
+      <c r="D78" s="9">
+        <v>300</v>
+      </c>
+      <c r="E78" s="9">
+        <v>0</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H78" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:8">
+      <c r="A79" s="7">
+        <v>103900101</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="8">
+        <v>10</v>
+      </c>
+      <c r="D79" s="9">
+        <v>15</v>
+      </c>
+      <c r="E79" s="9">
+        <v>0</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H79" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:8">
+      <c r="A80" s="7">
+        <v>103900102</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="8">
+        <v>20</v>
+      </c>
+      <c r="D80" s="9">
+        <v>25</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H80" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:8">
+      <c r="A81" s="7">
+        <v>103900103</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="8">
+        <v>50</v>
+      </c>
+      <c r="D81" s="9">
+        <v>60</v>
+      </c>
+      <c r="E81" s="9">
+        <v>0</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H81" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:8">
+      <c r="A82" s="7">
+        <v>103900104</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" s="8">
+        <v>250</v>
+      </c>
+      <c r="D82" s="9">
+        <v>300</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G82" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H82" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
     <cfRule type="duplicateValues" dxfId="0" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
     <cfRule type="duplicateValues" dxfId="0" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B79">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
     <cfRule type="duplicateValues" dxfId="0" priority="75"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71:A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75:A78">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79:A82">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
     <cfRule type="duplicateValues" dxfId="0" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
     <cfRule type="duplicateValues" dxfId="0" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
     <cfRule type="duplicateValues" dxfId="0" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:A61">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A65">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66:A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71:A74">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -384,6 +384,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -398,24 +410,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -3389,240 +3389,359 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="83" ht="16.5" spans="1:8">
+      <c r="A83" s="7">
+        <v>101600101</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="8">
+        <v>10</v>
+      </c>
+      <c r="D83" s="9">
+        <v>15</v>
+      </c>
+      <c r="E83" s="9">
+        <v>0</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H83" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="84" ht="16.5" spans="1:8">
+      <c r="A84" s="7">
+        <v>101600102</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="8">
+        <v>20</v>
+      </c>
+      <c r="D84" s="9">
+        <v>25</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G84" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H84" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" spans="1:8">
+      <c r="A85" s="7">
+        <v>101600103</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" s="8">
+        <v>50</v>
+      </c>
+      <c r="D85" s="9">
+        <v>60</v>
+      </c>
+      <c r="E85" s="9">
+        <v>0</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G85" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H85" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" spans="1:8">
+      <c r="A86" s="7">
+        <v>101600104</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="8">
+        <v>250</v>
+      </c>
+      <c r="D86" s="9">
+        <v>300</v>
+      </c>
+      <c r="E86" s="9">
+        <v>0</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H86" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="0" priority="90"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B79">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B86">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71:A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75:A78">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79:A82">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A83:A86">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B80">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B81">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B82">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:A61">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A65">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66:A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71:A74">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75:A78">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A79:A82">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -384,12 +384,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -399,6 +393,11 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -415,13 +414,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -3493,255 +3493,374 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="87" ht="16.5" spans="1:8">
+      <c r="A87" s="7">
+        <v>101500101</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="8">
+        <v>10</v>
+      </c>
+      <c r="D87" s="9">
+        <v>15</v>
+      </c>
+      <c r="E87" s="9">
+        <v>0</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H87" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="88" ht="16.5" spans="1:8">
+      <c r="A88" s="7">
+        <v>101500102</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="8">
+        <v>20</v>
+      </c>
+      <c r="D88" s="9">
+        <v>25</v>
+      </c>
+      <c r="E88" s="9">
+        <v>0</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H88" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="89" ht="16.5" spans="1:8">
+      <c r="A89" s="7">
+        <v>101500103</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="8">
+        <v>50</v>
+      </c>
+      <c r="D89" s="9">
+        <v>60</v>
+      </c>
+      <c r="E89" s="9">
+        <v>0</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H89" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="90" ht="16.5" spans="1:8">
+      <c r="A90" s="7">
+        <v>101500104</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="8">
+        <v>250</v>
+      </c>
+      <c r="D90" s="9">
+        <v>300</v>
+      </c>
+      <c r="E90" s="9">
+        <v>0</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H90" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="0" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B79">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B86">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B89">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B90">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71:A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75:A78">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79:A82">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A83:A86">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A87:A90">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B80">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B81">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B82">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B86">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:A61">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A65">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66:A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71:A74">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75:A78">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A79:A82">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A83:A86">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -386,29 +386,13 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -419,9 +403,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="9">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>25</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="7">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I13" s="15"/>
     </row>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="9">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>25</v>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="9">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="9">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>25</v>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -397,17 +397,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -422,6 +412,16 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -3597,270 +3597,389 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="91" ht="16.5" spans="1:8">
+      <c r="A91" s="7">
+        <v>102600101</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="8">
+        <v>10</v>
+      </c>
+      <c r="D91" s="9">
+        <v>15</v>
+      </c>
+      <c r="E91" s="9">
+        <v>0</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H91" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="92" ht="16.5" spans="1:8">
+      <c r="A92" s="7">
+        <v>102600102</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="8">
+        <v>20</v>
+      </c>
+      <c r="D92" s="9">
+        <v>25</v>
+      </c>
+      <c r="E92" s="9">
+        <v>0</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H92" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="93" ht="16.5" spans="1:8">
+      <c r="A93" s="7">
+        <v>102600103</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="8">
+        <v>50</v>
+      </c>
+      <c r="D93" s="9">
+        <v>60</v>
+      </c>
+      <c r="E93" s="9">
+        <v>0</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G93" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H93" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="94" ht="16.5" spans="1:8">
+      <c r="A94" s="7">
+        <v>102600104</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94" s="8">
+        <v>250</v>
+      </c>
+      <c r="D94" s="9">
+        <v>300</v>
+      </c>
+      <c r="E94" s="9">
+        <v>0</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H94" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="0" priority="100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B79">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B86">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B89">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B90">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B91">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B93">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B94">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71:A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75:A78">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79:A82">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A83:A86">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A87:A90">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A91:A94">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
     <cfRule type="duplicateValues" dxfId="0" priority="96"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B80">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B81">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B82">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B86">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:A61">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A65">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66:A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71:A74">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75:A78">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A79:A82">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A83:A86">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A87:A90">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B47">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -386,20 +386,8 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -415,8 +403,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -425,7 +425,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,6 +441,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,7 +782,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -800,16 +806,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -818,91 +824,91 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -940,6 +946,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
@@ -1382,7 +1400,7 @@
         <v>1700</v>
       </c>
       <c r="H5" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
@@ -1408,7 +1426,7 @@
         <v>1700</v>
       </c>
       <c r="H6" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -1434,7 +1452,7 @@
         <v>1700</v>
       </c>
       <c r="H7" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -1460,7 +1478,7 @@
         <v>1700</v>
       </c>
       <c r="H8" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
@@ -1485,8 +1503,8 @@
       <c r="G9" s="11">
         <v>0</v>
       </c>
-      <c r="H9" s="11">
-        <v>1500</v>
+      <c r="H9" s="7">
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
@@ -1511,8 +1529,8 @@
       <c r="G10" s="11">
         <v>0</v>
       </c>
-      <c r="H10" s="11">
-        <v>2500</v>
+      <c r="H10" s="7">
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
@@ -1537,8 +1555,8 @@
       <c r="G11" s="11">
         <v>0</v>
       </c>
-      <c r="H11" s="11">
-        <v>6000</v>
+      <c r="H11" s="7">
+        <v>60</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -1563,63 +1581,63 @@
       <c r="G12" s="11">
         <v>0</v>
       </c>
-      <c r="H12" s="11">
-        <v>30000</v>
+      <c r="H12" s="7">
+        <v>300</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
       <c r="A13" s="7">
         <v>101200101</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="C13" s="16">
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
         <v>1000</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="7">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7">
+      <c r="G13" s="15">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15">
         <v>1</v>
       </c>
-      <c r="I13" s="15"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="7">
         <v>101400101</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="C14" s="16">
+        <v>0</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0</v>
+      </c>
+      <c r="E14" s="17">
         <v>1000</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
-        <v>50</v>
-      </c>
-      <c r="I14" s="15"/>
+      <c r="G14" s="15">
+        <v>0</v>
+      </c>
+      <c r="H14" s="15">
+        <v>1</v>
+      </c>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" ht="16.5" spans="1:9">
       <c r="A15" s="7">
@@ -1644,7 +1662,7 @@
         <v>1700</v>
       </c>
       <c r="H15" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -1670,7 +1688,7 @@
         <v>1700</v>
       </c>
       <c r="H16" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -1696,7 +1714,7 @@
         <v>1700</v>
       </c>
       <c r="H17" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -1722,7 +1740,7 @@
         <v>1700</v>
       </c>
       <c r="H18" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -1748,7 +1766,7 @@
         <v>1700</v>
       </c>
       <c r="H19" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -1774,7 +1792,7 @@
         <v>1700</v>
       </c>
       <c r="H20" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -1800,7 +1818,7 @@
         <v>1700</v>
       </c>
       <c r="H21" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -1826,7 +1844,7 @@
         <v>1700</v>
       </c>
       <c r="H22" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -1852,7 +1870,7 @@
         <v>1700</v>
       </c>
       <c r="H23" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -1878,7 +1896,7 @@
         <v>1700</v>
       </c>
       <c r="H24" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:8">
@@ -1904,7 +1922,7 @@
         <v>1700</v>
       </c>
       <c r="H25" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:8">
@@ -1930,7 +1948,7 @@
         <v>1700</v>
       </c>
       <c r="H26" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:8">
@@ -1956,7 +1974,7 @@
         <v>1700</v>
       </c>
       <c r="H27" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:8">
@@ -1982,7 +2000,7 @@
         <v>1700</v>
       </c>
       <c r="H28" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:8">
@@ -2008,7 +2026,7 @@
         <v>1700</v>
       </c>
       <c r="H29" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:8">
@@ -2034,7 +2052,7 @@
         <v>1700</v>
       </c>
       <c r="H30" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:8">
@@ -2060,7 +2078,7 @@
         <v>1700</v>
       </c>
       <c r="H31" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:8">
@@ -2086,7 +2104,7 @@
         <v>1700</v>
       </c>
       <c r="H32" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:8">
@@ -2112,7 +2130,7 @@
         <v>1700</v>
       </c>
       <c r="H33" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:8">
@@ -2138,7 +2156,7 @@
         <v>1700</v>
       </c>
       <c r="H34" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:8">
@@ -2164,7 +2182,7 @@
         <v>1700</v>
       </c>
       <c r="H35" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:8">
@@ -2190,7 +2208,7 @@
         <v>1700</v>
       </c>
       <c r="H36" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:8">
@@ -2216,7 +2234,7 @@
         <v>1700</v>
       </c>
       <c r="H37" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:8">
@@ -2242,7 +2260,7 @@
         <v>1700</v>
       </c>
       <c r="H38" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:8">
@@ -2268,7 +2286,7 @@
         <v>1700</v>
       </c>
       <c r="H39" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:8">
@@ -2294,7 +2312,7 @@
         <v>1700</v>
       </c>
       <c r="H40" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:8">
@@ -2320,7 +2338,7 @@
         <v>1700</v>
       </c>
       <c r="H41" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:8">
@@ -2346,33 +2364,33 @@
         <v>1700</v>
       </c>
       <c r="H42" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:8">
       <c r="A43" s="7">
         <v>103400101</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="8">
-        <v>0</v>
-      </c>
-      <c r="D43" s="9">
-        <v>0</v>
-      </c>
-      <c r="E43" s="9">
+      <c r="C43" s="16">
+        <v>0</v>
+      </c>
+      <c r="D43" s="17">
+        <v>0</v>
+      </c>
+      <c r="E43" s="17">
         <v>1000</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="7">
-        <v>0</v>
-      </c>
-      <c r="H43" s="7">
-        <v>50</v>
+      <c r="G43" s="15">
+        <v>0</v>
+      </c>
+      <c r="H43" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:8">
@@ -2398,7 +2416,7 @@
         <v>1700</v>
       </c>
       <c r="H44" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:8">
@@ -2424,7 +2442,7 @@
         <v>1700</v>
       </c>
       <c r="H45" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:8">
@@ -2450,7 +2468,7 @@
         <v>1700</v>
       </c>
       <c r="H46" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:8">
@@ -2476,7 +2494,7 @@
         <v>1700</v>
       </c>
       <c r="H47" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:8">
@@ -2502,7 +2520,7 @@
         <v>1700</v>
       </c>
       <c r="H48" s="7">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:8">
@@ -2528,7 +2546,7 @@
         <v>1700</v>
       </c>
       <c r="H49" s="7">
-        <v>2500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:8">
@@ -2554,7 +2572,7 @@
         <v>1700</v>
       </c>
       <c r="H50" s="7">
-        <v>6000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:8">
@@ -2580,33 +2598,33 @@
         <v>1700</v>
       </c>
       <c r="H51" s="7">
-        <v>30000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:8">
       <c r="A52" s="7">
         <v>103600101</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="8">
-        <v>0</v>
-      </c>
-      <c r="D52" s="9">
-        <v>0</v>
-      </c>
-      <c r="E52" s="9">
+      <c r="C52" s="16">
+        <v>0</v>
+      </c>
+      <c r="D52" s="17">
+        <v>0</v>
+      </c>
+      <c r="E52" s="17">
         <v>1000</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G52" s="7">
-        <v>0</v>
-      </c>
-      <c r="H52" s="7">
-        <v>50</v>
+      <c r="G52" s="15">
+        <v>0</v>
+      </c>
+      <c r="H52" s="15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="14865" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="29">
   <si>
     <t>奖池ID</t>
   </si>
@@ -384,13 +384,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -409,14 +409,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -3701,6 +3701,214 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="95" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A95" s="7">
+        <v>105000101</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="8">
+        <v>10</v>
+      </c>
+      <c r="D95" s="9">
+        <v>15</v>
+      </c>
+      <c r="E95" s="9">
+        <v>0</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H95" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A96" s="7">
+        <v>105000102</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="8">
+        <v>20</v>
+      </c>
+      <c r="D96" s="9">
+        <v>25</v>
+      </c>
+      <c r="E96" s="9">
+        <v>0</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H96" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A97" s="7">
+        <v>105000103</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="8">
+        <v>50</v>
+      </c>
+      <c r="D97" s="9">
+        <v>60</v>
+      </c>
+      <c r="E97" s="9">
+        <v>0</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G97" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H97" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A98" s="7">
+        <v>105000104</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C98" s="8">
+        <v>250</v>
+      </c>
+      <c r="D98" s="9">
+        <v>300</v>
+      </c>
+      <c r="E98" s="9">
+        <v>0</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H98" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A99" s="7">
+        <v>105100101</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="8">
+        <v>10</v>
+      </c>
+      <c r="D99" s="9">
+        <v>15</v>
+      </c>
+      <c r="E99" s="9">
+        <v>0</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H99" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A100" s="7">
+        <v>105100102</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="8">
+        <v>20</v>
+      </c>
+      <c r="D100" s="9">
+        <v>25</v>
+      </c>
+      <c r="E100" s="9">
+        <v>0</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G100" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H100" s="7">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A101" s="7">
+        <v>105100103</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="8">
+        <v>50</v>
+      </c>
+      <c r="D101" s="9">
+        <v>60</v>
+      </c>
+      <c r="E101" s="9">
+        <v>0</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G101" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H101" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A102" s="7">
+        <v>105100104</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C102" s="8">
+        <v>250</v>
+      </c>
+      <c r="D102" s="9">
+        <v>300</v>
+      </c>
+      <c r="E102" s="9">
+        <v>0</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" s="7">
+        <v>1700</v>
+      </c>
+      <c r="H102" s="7">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
     <cfRule type="duplicateValues" dxfId="0" priority="105"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21000" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="30">
   <si>
     <t>奖池ID</t>
   </si>
@@ -211,6 +211,9 @@
   <si>
     <t>3【夺宝】分散中50%大奖</t>
   </si>
+  <si>
+    <t>1【奖池符号】分散中50%大奖</t>
+  </si>
 </sst>
 </file>
 
@@ -224,13 +227,19 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -386,30 +395,19 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -422,6 +420,17 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -631,7 +640,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -652,6 +661,32 @@
       <bottom style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -770,180 +805,187 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1277,7 +1319,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1285,33 +1327,33 @@
     <col min="3" max="3" width="18.75" customWidth="1"/>
     <col min="4" max="4" width="20.75" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="20.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
     <col min="8" max="8" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="9" style="2"/>
+    <col min="9" max="9" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1328,7 +1370,7 @@
       <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G2" t="s">
@@ -1351,10 +1393,10 @@
       <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
@@ -1362,2562 +1404,2900 @@
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>100100101</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>10</v>
       </c>
-      <c r="D5" s="10">
-        <v>15</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="11">
+        <v>15</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="G5" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H5" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>100100102</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="9">
-        <v>20</v>
-      </c>
-      <c r="D6" s="10">
-        <v>25</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="C6" s="10">
+        <v>20</v>
+      </c>
+      <c r="D6" s="11">
+        <v>25</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="G6" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H6" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <v>100100103</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="10">
         <v>50</v>
       </c>
-      <c r="D7" s="10">
-        <v>60</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="11" t="s">
+      <c r="D7" s="11">
+        <v>60</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H7" s="8">
+      <c r="G7" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H7" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="8">
+      <c r="A8" s="9">
         <v>100100104</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <v>250</v>
       </c>
-      <c r="D8" s="10">
-        <v>300</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11" t="s">
+      <c r="D8" s="11">
+        <v>300</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="G8" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H8" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>100300101</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>10</v>
       </c>
-      <c r="D9" s="14">
-        <v>15</v>
-      </c>
-      <c r="E9" s="14">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15" t="s">
+      <c r="D9" s="15">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="12">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12">
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
         <v>15</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>100300102</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="13">
-        <v>20</v>
-      </c>
-      <c r="D10" s="14">
-        <v>25</v>
-      </c>
-      <c r="E10" s="14">
-        <v>0</v>
-      </c>
-      <c r="F10" s="15" t="s">
+      <c r="C10" s="14">
+        <v>20</v>
+      </c>
+      <c r="D10" s="15">
+        <v>25</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="12">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12">
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>100300103</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="13">
+      <c r="B11" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="14">
         <v>50</v>
       </c>
-      <c r="D11" s="14">
-        <v>60</v>
-      </c>
-      <c r="E11" s="14">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="s">
+      <c r="D11" s="15">
+        <v>60</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="12">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12">
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
         <v>60</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>100300104</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <v>250</v>
       </c>
-      <c r="D12" s="14">
-        <v>300</v>
-      </c>
-      <c r="E12" s="14">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15" t="s">
+      <c r="D12" s="15">
+        <v>300</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
         <v>300</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
-      <c r="A13" s="8">
+      <c r="A13" s="9">
         <v>101200101</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10">
+      <c r="C13" s="10">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11">
         <v>1000</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="F13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
         <v>1</v>
       </c>
-      <c r="I13" s="16"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" ht="16.5" spans="1:9">
-      <c r="A14" s="8">
+      <c r="A14" s="9">
         <v>101400101</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="9">
-        <v>0</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0</v>
-      </c>
-      <c r="E14" s="10">
+      <c r="C14" s="10">
+        <v>0</v>
+      </c>
+      <c r="D14" s="11">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11">
         <v>1000</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="F14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
         <v>1</v>
       </c>
-      <c r="I14" s="16"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" ht="16.5" spans="1:9">
-      <c r="A15" s="8">
+      <c r="A15" s="9">
         <v>102400101</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <v>10</v>
       </c>
-      <c r="D15" s="10">
-        <v>15</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0</v>
-      </c>
-      <c r="F15" s="11" t="s">
+      <c r="D15" s="11">
+        <v>15</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="G15" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H15" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
-      <c r="A16" s="8">
+      <c r="A16" s="9">
         <v>102400102</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="9">
-        <v>20</v>
-      </c>
-      <c r="D16" s="10">
-        <v>25</v>
-      </c>
-      <c r="E16" s="10">
-        <v>0</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="C16" s="10">
+        <v>20</v>
+      </c>
+      <c r="D16" s="11">
+        <v>25</v>
+      </c>
+      <c r="E16" s="11">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H16" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
-      <c r="A17" s="8">
+      <c r="A17" s="9">
         <v>102400103</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="9">
+      <c r="B17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="10">
         <v>50</v>
       </c>
-      <c r="D17" s="10">
-        <v>60</v>
-      </c>
-      <c r="E17" s="10">
-        <v>0</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="D17" s="11">
+        <v>60</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="G17" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H17" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
-      <c r="A18" s="8">
+      <c r="A18" s="9">
         <v>102400104</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="10">
         <v>250</v>
       </c>
-      <c r="D18" s="10">
-        <v>300</v>
-      </c>
-      <c r="E18" s="10">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="s">
+      <c r="D18" s="11">
+        <v>300</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="G18" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H18" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
-      <c r="A19" s="8">
+      <c r="A19" s="9">
         <v>101700101</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="10">
         <v>10</v>
       </c>
-      <c r="D19" s="10">
-        <v>15</v>
-      </c>
-      <c r="E19" s="10">
-        <v>0</v>
-      </c>
-      <c r="F19" s="11" t="s">
+      <c r="D19" s="11">
+        <v>15</v>
+      </c>
+      <c r="E19" s="11">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="G19" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H19" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
-      <c r="A20" s="8">
+      <c r="A20" s="9">
         <v>101700102</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9">
-        <v>20</v>
-      </c>
-      <c r="D20" s="10">
-        <v>25</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0</v>
-      </c>
-      <c r="F20" s="11" t="s">
+      <c r="C20" s="10">
+        <v>20</v>
+      </c>
+      <c r="D20" s="11">
+        <v>25</v>
+      </c>
+      <c r="E20" s="11">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H20" s="8">
+      <c r="G20" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H20" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
-      <c r="A21" s="8">
+      <c r="A21" s="9">
         <v>101700103</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="10">
         <v>50</v>
       </c>
-      <c r="D21" s="10">
-        <v>60</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0</v>
-      </c>
-      <c r="F21" s="11" t="s">
+      <c r="D21" s="11">
+        <v>60</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H21" s="8">
+      <c r="G21" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H21" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
-      <c r="A22" s="8">
+      <c r="A22" s="9">
         <v>101700104</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="10">
         <v>250</v>
       </c>
-      <c r="D22" s="10">
-        <v>300</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0</v>
-      </c>
-      <c r="F22" s="11" t="s">
+      <c r="D22" s="11">
+        <v>300</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H22" s="8">
+      <c r="G22" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H22" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
-      <c r="A23" s="8">
+      <c r="A23" s="9">
         <v>102200101</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="10">
         <v>10</v>
       </c>
-      <c r="D23" s="10">
-        <v>15</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0</v>
-      </c>
-      <c r="F23" s="11" t="s">
+      <c r="D23" s="11">
+        <v>15</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H23" s="8">
+      <c r="G23" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H23" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
-      <c r="A24" s="8">
+      <c r="A24" s="9">
         <v>102200102</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="9">
-        <v>20</v>
-      </c>
-      <c r="D24" s="10">
-        <v>25</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="C24" s="10">
+        <v>20</v>
+      </c>
+      <c r="D24" s="11">
+        <v>25</v>
+      </c>
+      <c r="E24" s="11">
+        <v>0</v>
+      </c>
+      <c r="F24" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H24" s="8">
+      <c r="G24" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H24" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:8">
-      <c r="A25" s="8">
+      <c r="A25" s="9">
         <v>102200103</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="9">
+      <c r="B25" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="10">
         <v>50</v>
       </c>
-      <c r="D25" s="10">
-        <v>60</v>
-      </c>
-      <c r="E25" s="10">
-        <v>0</v>
-      </c>
-      <c r="F25" s="11" t="s">
+      <c r="D25" s="11">
+        <v>60</v>
+      </c>
+      <c r="E25" s="11">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H25" s="8">
+      <c r="G25" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H25" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:8">
-      <c r="A26" s="8">
+      <c r="A26" s="9">
         <v>102200104</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <v>250</v>
       </c>
-      <c r="D26" s="10">
-        <v>300</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0</v>
-      </c>
-      <c r="F26" s="11" t="s">
+      <c r="D26" s="11">
+        <v>300</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0</v>
+      </c>
+      <c r="F26" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H26" s="8">
+      <c r="G26" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H26" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:8">
-      <c r="A27" s="8">
+      <c r="A27" s="9">
         <v>102100101</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <v>10</v>
       </c>
-      <c r="D27" s="10">
-        <v>15</v>
-      </c>
-      <c r="E27" s="10">
-        <v>0</v>
-      </c>
-      <c r="F27" s="11" t="s">
+      <c r="D27" s="11">
+        <v>15</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0</v>
+      </c>
+      <c r="F27" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G27" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H27" s="8">
+      <c r="G27" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H27" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:8">
-      <c r="A28" s="8">
+      <c r="A28" s="9">
         <v>102100102</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="9">
-        <v>20</v>
-      </c>
-      <c r="D28" s="10">
-        <v>25</v>
-      </c>
-      <c r="E28" s="10">
-        <v>0</v>
-      </c>
-      <c r="F28" s="11" t="s">
+      <c r="C28" s="10">
+        <v>20</v>
+      </c>
+      <c r="D28" s="11">
+        <v>25</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H28" s="8">
+      <c r="G28" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H28" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:8">
-      <c r="A29" s="8">
+      <c r="A29" s="9">
         <v>102100103</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="9">
+      <c r="B29" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="10">
         <v>50</v>
       </c>
-      <c r="D29" s="10">
-        <v>60</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0</v>
-      </c>
-      <c r="F29" s="11" t="s">
+      <c r="D29" s="11">
+        <v>60</v>
+      </c>
+      <c r="E29" s="11">
+        <v>0</v>
+      </c>
+      <c r="F29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H29" s="8">
+      <c r="G29" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H29" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:8">
-      <c r="A30" s="8">
+      <c r="A30" s="9">
         <v>102100104</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="10">
         <v>250</v>
       </c>
-      <c r="D30" s="10">
-        <v>300</v>
-      </c>
-      <c r="E30" s="10">
-        <v>0</v>
-      </c>
-      <c r="F30" s="11" t="s">
+      <c r="D30" s="11">
+        <v>300</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0</v>
+      </c>
+      <c r="F30" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G30" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H30" s="8">
+      <c r="G30" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H30" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:8">
-      <c r="A31" s="8">
+      <c r="A31" s="9">
         <v>101800101</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="10">
         <v>10</v>
       </c>
-      <c r="D31" s="10">
-        <v>15</v>
-      </c>
-      <c r="E31" s="10">
-        <v>0</v>
-      </c>
-      <c r="F31" s="11" t="s">
+      <c r="D31" s="11">
+        <v>15</v>
+      </c>
+      <c r="E31" s="11">
+        <v>0</v>
+      </c>
+      <c r="F31" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H31" s="8">
+      <c r="G31" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H31" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:8">
-      <c r="A32" s="8">
+      <c r="A32" s="9">
         <v>101800102</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="9">
-        <v>20</v>
-      </c>
-      <c r="D32" s="10">
-        <v>25</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0</v>
-      </c>
-      <c r="F32" s="11" t="s">
+      <c r="C32" s="10">
+        <v>20</v>
+      </c>
+      <c r="D32" s="11">
+        <v>25</v>
+      </c>
+      <c r="E32" s="11">
+        <v>0</v>
+      </c>
+      <c r="F32" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G32" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H32" s="8">
+      <c r="G32" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H32" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:8">
-      <c r="A33" s="8">
+      <c r="A33" s="9">
         <v>101800103</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="9">
+      <c r="B33" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="10">
         <v>50</v>
       </c>
-      <c r="D33" s="10">
-        <v>60</v>
-      </c>
-      <c r="E33" s="10">
-        <v>0</v>
-      </c>
-      <c r="F33" s="11" t="s">
+      <c r="D33" s="11">
+        <v>60</v>
+      </c>
+      <c r="E33" s="11">
+        <v>0</v>
+      </c>
+      <c r="F33" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G33" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H33" s="8">
+      <c r="G33" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H33" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:8">
-      <c r="A34" s="8">
+      <c r="A34" s="9">
         <v>101800104</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <v>250</v>
       </c>
-      <c r="D34" s="10">
-        <v>300</v>
-      </c>
-      <c r="E34" s="10">
-        <v>0</v>
-      </c>
-      <c r="F34" s="11" t="s">
+      <c r="D34" s="11">
+        <v>300</v>
+      </c>
+      <c r="E34" s="11">
+        <v>0</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H34" s="8">
+      <c r="G34" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H34" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:8">
-      <c r="A35" s="8">
+      <c r="A35" s="9">
         <v>102500101</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="10">
         <v>10</v>
       </c>
-      <c r="D35" s="10">
-        <v>15</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0</v>
-      </c>
-      <c r="F35" s="11" t="s">
+      <c r="D35" s="11">
+        <v>15</v>
+      </c>
+      <c r="E35" s="11">
+        <v>0</v>
+      </c>
+      <c r="F35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H35" s="8">
+      <c r="G35" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H35" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:8">
-      <c r="A36" s="8">
+      <c r="A36" s="9">
         <v>102500102</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="9">
-        <v>20</v>
-      </c>
-      <c r="D36" s="10">
-        <v>25</v>
-      </c>
-      <c r="E36" s="10">
-        <v>0</v>
-      </c>
-      <c r="F36" s="11" t="s">
+      <c r="C36" s="10">
+        <v>20</v>
+      </c>
+      <c r="D36" s="11">
+        <v>25</v>
+      </c>
+      <c r="E36" s="11">
+        <v>0</v>
+      </c>
+      <c r="F36" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H36" s="8">
+      <c r="G36" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H36" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:8">
-      <c r="A37" s="8">
+      <c r="A37" s="9">
         <v>102500103</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="9">
+      <c r="B37" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="10">
         <v>50</v>
       </c>
-      <c r="D37" s="10">
-        <v>60</v>
-      </c>
-      <c r="E37" s="10">
-        <v>0</v>
-      </c>
-      <c r="F37" s="11" t="s">
+      <c r="D37" s="11">
+        <v>60</v>
+      </c>
+      <c r="E37" s="11">
+        <v>0</v>
+      </c>
+      <c r="F37" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H37" s="8">
+      <c r="G37" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H37" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:8">
-      <c r="A38" s="8">
+      <c r="A38" s="9">
         <v>102500104</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="10">
         <v>250</v>
       </c>
-      <c r="D38" s="10">
-        <v>300</v>
-      </c>
-      <c r="E38" s="10">
-        <v>0</v>
-      </c>
-      <c r="F38" s="11" t="s">
+      <c r="D38" s="11">
+        <v>300</v>
+      </c>
+      <c r="E38" s="11">
+        <v>0</v>
+      </c>
+      <c r="F38" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G38" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H38" s="8">
+      <c r="G38" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H38" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:8">
-      <c r="A39" s="8">
+      <c r="A39" s="9">
         <v>102300101</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="10">
         <v>10</v>
       </c>
-      <c r="D39" s="10">
-        <v>15</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0</v>
-      </c>
-      <c r="F39" s="11" t="s">
+      <c r="D39" s="11">
+        <v>15</v>
+      </c>
+      <c r="E39" s="11">
+        <v>0</v>
+      </c>
+      <c r="F39" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H39" s="8">
+      <c r="G39" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H39" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:8">
-      <c r="A40" s="8">
+      <c r="A40" s="9">
         <v>102300102</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="9">
-        <v>20</v>
-      </c>
-      <c r="D40" s="10">
-        <v>25</v>
-      </c>
-      <c r="E40" s="10">
-        <v>0</v>
-      </c>
-      <c r="F40" s="11" t="s">
+      <c r="C40" s="10">
+        <v>20</v>
+      </c>
+      <c r="D40" s="11">
+        <v>25</v>
+      </c>
+      <c r="E40" s="11">
+        <v>0</v>
+      </c>
+      <c r="F40" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G40" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H40" s="8">
+      <c r="G40" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H40" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:8">
-      <c r="A41" s="8">
+      <c r="A41" s="9">
         <v>102300103</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="9">
+      <c r="B41" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="10">
         <v>50</v>
       </c>
-      <c r="D41" s="10">
-        <v>60</v>
-      </c>
-      <c r="E41" s="10">
-        <v>0</v>
-      </c>
-      <c r="F41" s="11" t="s">
+      <c r="D41" s="11">
+        <v>60</v>
+      </c>
+      <c r="E41" s="11">
+        <v>0</v>
+      </c>
+      <c r="F41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G41" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H41" s="8">
+      <c r="G41" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H41" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:8">
-      <c r="A42" s="8">
+      <c r="A42" s="9">
         <v>102300104</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="10">
         <v>250</v>
       </c>
-      <c r="D42" s="10">
-        <v>300</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0</v>
-      </c>
-      <c r="F42" s="11" t="s">
+      <c r="D42" s="11">
+        <v>300</v>
+      </c>
+      <c r="E42" s="11">
+        <v>0</v>
+      </c>
+      <c r="F42" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G42" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H42" s="8">
+      <c r="G42" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H42" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:8">
-      <c r="A43" s="8">
+      <c r="A43" s="9">
         <v>103400101</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="9">
-        <v>0</v>
-      </c>
-      <c r="D43" s="10">
-        <v>0</v>
-      </c>
-      <c r="E43" s="10">
+      <c r="C43" s="10">
+        <v>0</v>
+      </c>
+      <c r="D43" s="11">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11">
         <v>1000</v>
       </c>
-      <c r="F43" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G43" s="8">
-        <v>0</v>
-      </c>
-      <c r="H43" s="8">
+      <c r="F43" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:8">
-      <c r="A44" s="8">
+      <c r="A44" s="9">
         <v>103401101</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C44" s="9">
-        <v>0</v>
-      </c>
-      <c r="D44" s="10">
-        <v>0</v>
-      </c>
-      <c r="E44" s="10">
+      <c r="C44" s="10">
+        <v>0</v>
+      </c>
+      <c r="D44" s="11">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11">
         <v>1000</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G44" s="8">
-        <v>0</v>
-      </c>
-      <c r="H44" s="8">
+      <c r="F44" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0</v>
+      </c>
+      <c r="H44" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:8">
-      <c r="A45" s="8">
+      <c r="A45" s="9">
         <v>103500101</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="10">
         <v>10</v>
       </c>
-      <c r="D45" s="10">
-        <v>15</v>
-      </c>
-      <c r="E45" s="10">
-        <v>0</v>
-      </c>
-      <c r="F45" s="11" t="s">
+      <c r="D45" s="11">
+        <v>15</v>
+      </c>
+      <c r="E45" s="11">
+        <v>0</v>
+      </c>
+      <c r="F45" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H45" s="8">
+      <c r="G45" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H45" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:8">
-      <c r="A46" s="8">
+      <c r="A46" s="9">
         <v>103500102</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="9">
-        <v>20</v>
-      </c>
-      <c r="D46" s="10">
-        <v>25</v>
-      </c>
-      <c r="E46" s="10">
-        <v>0</v>
-      </c>
-      <c r="F46" s="11" t="s">
+      <c r="C46" s="10">
+        <v>20</v>
+      </c>
+      <c r="D46" s="11">
+        <v>25</v>
+      </c>
+      <c r="E46" s="11">
+        <v>0</v>
+      </c>
+      <c r="F46" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G46" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H46" s="8">
+      <c r="G46" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H46" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:8">
-      <c r="A47" s="8">
+      <c r="A47" s="9">
         <v>103500103</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="9">
+      <c r="B47" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="10">
         <v>50</v>
       </c>
-      <c r="D47" s="10">
-        <v>60</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="D47" s="11">
+        <v>60</v>
+      </c>
+      <c r="E47" s="11">
+        <v>0</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G47" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H47" s="8">
+      <c r="G47" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H47" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:8">
-      <c r="A48" s="8">
+      <c r="A48" s="9">
         <v>103500104</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="10">
         <v>250</v>
       </c>
-      <c r="D48" s="10">
-        <v>300</v>
-      </c>
-      <c r="E48" s="10">
-        <v>0</v>
-      </c>
-      <c r="F48" s="11" t="s">
+      <c r="D48" s="11">
+        <v>300</v>
+      </c>
+      <c r="E48" s="11">
+        <v>0</v>
+      </c>
+      <c r="F48" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G48" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H48" s="8">
+      <c r="G48" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H48" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:8">
-      <c r="A49" s="8">
+      <c r="A49" s="9">
         <v>103501101</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="10">
         <v>10</v>
       </c>
-      <c r="D49" s="10">
-        <v>15</v>
-      </c>
-      <c r="E49" s="10">
-        <v>0</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="D49" s="11">
+        <v>15</v>
+      </c>
+      <c r="E49" s="11">
+        <v>0</v>
+      </c>
+      <c r="F49" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G49" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H49" s="8">
+      <c r="G49" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H49" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:8">
-      <c r="A50" s="8">
+      <c r="A50" s="9">
         <v>103501102</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="9">
-        <v>20</v>
-      </c>
-      <c r="D50" s="10">
-        <v>25</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0</v>
-      </c>
-      <c r="F50" s="11" t="s">
+      <c r="C50" s="10">
+        <v>20</v>
+      </c>
+      <c r="D50" s="11">
+        <v>25</v>
+      </c>
+      <c r="E50" s="11">
+        <v>0</v>
+      </c>
+      <c r="F50" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G50" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H50" s="8">
+      <c r="G50" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H50" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:8">
-      <c r="A51" s="8">
+      <c r="A51" s="9">
         <v>103501103</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="9">
+      <c r="B51" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="10">
         <v>50</v>
       </c>
-      <c r="D51" s="10">
-        <v>60</v>
-      </c>
-      <c r="E51" s="10">
-        <v>0</v>
-      </c>
-      <c r="F51" s="11" t="s">
+      <c r="D51" s="11">
+        <v>60</v>
+      </c>
+      <c r="E51" s="11">
+        <v>0</v>
+      </c>
+      <c r="F51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H51" s="8">
+      <c r="G51" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H51" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:8">
-      <c r="A52" s="8">
+      <c r="A52" s="9">
         <v>103501104</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="10">
         <v>250</v>
       </c>
-      <c r="D52" s="10">
-        <v>300</v>
-      </c>
-      <c r="E52" s="10">
-        <v>0</v>
-      </c>
-      <c r="F52" s="11" t="s">
+      <c r="D52" s="11">
+        <v>300</v>
+      </c>
+      <c r="E52" s="11">
+        <v>0</v>
+      </c>
+      <c r="F52" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G52" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H52" s="8">
+      <c r="G52" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H52" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:8">
-      <c r="A53" s="8">
+      <c r="A53" s="9">
         <v>103600101</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C53" s="9">
-        <v>0</v>
-      </c>
-      <c r="D53" s="10">
-        <v>0</v>
-      </c>
-      <c r="E53" s="10">
+      <c r="C53" s="10">
+        <v>0</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0</v>
+      </c>
+      <c r="E53" s="11">
         <v>1000</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" s="8">
-        <v>0</v>
-      </c>
-      <c r="H53" s="8">
+      <c r="F53" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:8">
-      <c r="A54" s="8">
+      <c r="A54" s="9">
         <v>102800101</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="10">
         <v>10</v>
       </c>
-      <c r="D54" s="10">
-        <v>15</v>
-      </c>
-      <c r="E54" s="10">
-        <v>0</v>
-      </c>
-      <c r="F54" s="11" t="s">
+      <c r="D54" s="11">
+        <v>15</v>
+      </c>
+      <c r="E54" s="11">
+        <v>0</v>
+      </c>
+      <c r="F54" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G54" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H54" s="8">
+      <c r="G54" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H54" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:8">
-      <c r="A55" s="8">
+      <c r="A55" s="9">
         <v>102800102</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="9">
-        <v>20</v>
-      </c>
-      <c r="D55" s="10">
-        <v>25</v>
-      </c>
-      <c r="E55" s="10">
-        <v>0</v>
-      </c>
-      <c r="F55" s="11" t="s">
+      <c r="C55" s="10">
+        <v>20</v>
+      </c>
+      <c r="D55" s="11">
+        <v>25</v>
+      </c>
+      <c r="E55" s="11">
+        <v>0</v>
+      </c>
+      <c r="F55" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H55" s="8">
+      <c r="G55" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H55" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:8">
-      <c r="A56" s="8">
+      <c r="A56" s="9">
         <v>102800103</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="9">
+      <c r="B56" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="10">
         <v>50</v>
       </c>
-      <c r="D56" s="10">
-        <v>60</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0</v>
-      </c>
-      <c r="F56" s="11" t="s">
+      <c r="D56" s="11">
+        <v>60</v>
+      </c>
+      <c r="E56" s="11">
+        <v>0</v>
+      </c>
+      <c r="F56" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H56" s="8">
+      <c r="G56" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H56" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:8">
-      <c r="A57" s="8">
+      <c r="A57" s="9">
         <v>102800104</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="10">
         <v>250</v>
       </c>
-      <c r="D57" s="10">
-        <v>300</v>
-      </c>
-      <c r="E57" s="10">
-        <v>0</v>
-      </c>
-      <c r="F57" s="11" t="s">
+      <c r="D57" s="11">
+        <v>300</v>
+      </c>
+      <c r="E57" s="11">
+        <v>0</v>
+      </c>
+      <c r="F57" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G57" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H57" s="8">
+      <c r="G57" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H57" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:8">
-      <c r="A58" s="8">
+      <c r="A58" s="9">
         <v>102000101</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="10">
         <v>10</v>
       </c>
-      <c r="D58" s="10">
-        <v>15</v>
-      </c>
-      <c r="E58" s="10">
-        <v>0</v>
-      </c>
-      <c r="F58" s="11" t="s">
+      <c r="D58" s="11">
+        <v>15</v>
+      </c>
+      <c r="E58" s="11">
+        <v>0</v>
+      </c>
+      <c r="F58" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G58" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H58" s="8">
+      <c r="G58" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H58" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:8">
-      <c r="A59" s="8">
+      <c r="A59" s="9">
         <v>102000102</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="9">
-        <v>20</v>
-      </c>
-      <c r="D59" s="10">
-        <v>25</v>
-      </c>
-      <c r="E59" s="10">
-        <v>0</v>
-      </c>
-      <c r="F59" s="11" t="s">
+      <c r="C59" s="10">
+        <v>20</v>
+      </c>
+      <c r="D59" s="11">
+        <v>25</v>
+      </c>
+      <c r="E59" s="11">
+        <v>0</v>
+      </c>
+      <c r="F59" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H59" s="8">
+      <c r="G59" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H59" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:8">
-      <c r="A60" s="8">
+      <c r="A60" s="9">
         <v>102000103</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="9">
+      <c r="B60" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="10">
         <v>50</v>
       </c>
-      <c r="D60" s="10">
-        <v>60</v>
-      </c>
-      <c r="E60" s="10">
-        <v>0</v>
-      </c>
-      <c r="F60" s="11" t="s">
+      <c r="D60" s="11">
+        <v>60</v>
+      </c>
+      <c r="E60" s="11">
+        <v>0</v>
+      </c>
+      <c r="F60" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H60" s="8">
+      <c r="G60" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H60" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:8">
-      <c r="A61" s="8">
+      <c r="A61" s="9">
         <v>102000104</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="10">
         <v>250</v>
       </c>
-      <c r="D61" s="10">
-        <v>300</v>
-      </c>
-      <c r="E61" s="10">
-        <v>0</v>
-      </c>
-      <c r="F61" s="11" t="s">
+      <c r="D61" s="11">
+        <v>300</v>
+      </c>
+      <c r="E61" s="11">
+        <v>0</v>
+      </c>
+      <c r="F61" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G61" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H61" s="8">
+      <c r="G61" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H61" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:8">
-      <c r="A62" s="8">
+      <c r="A62" s="9">
         <v>103800101</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="10">
         <v>10</v>
       </c>
-      <c r="D62" s="10">
-        <v>15</v>
-      </c>
-      <c r="E62" s="10">
-        <v>0</v>
-      </c>
-      <c r="F62" s="11" t="s">
+      <c r="D62" s="11">
+        <v>15</v>
+      </c>
+      <c r="E62" s="11">
+        <v>0</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G62" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H62" s="8">
+      <c r="G62" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H62" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:8">
-      <c r="A63" s="8">
+      <c r="A63" s="9">
         <v>103800102</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C63" s="9">
-        <v>20</v>
-      </c>
-      <c r="D63" s="10">
-        <v>25</v>
-      </c>
-      <c r="E63" s="10">
-        <v>0</v>
-      </c>
-      <c r="F63" s="11" t="s">
+      <c r="C63" s="10">
+        <v>20</v>
+      </c>
+      <c r="D63" s="11">
+        <v>25</v>
+      </c>
+      <c r="E63" s="11">
+        <v>0</v>
+      </c>
+      <c r="F63" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G63" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H63" s="8">
+      <c r="G63" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H63" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:8">
-      <c r="A64" s="8">
+      <c r="A64" s="9">
         <v>103800103</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="9">
+      <c r="B64" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="10">
         <v>50</v>
       </c>
-      <c r="D64" s="10">
-        <v>60</v>
-      </c>
-      <c r="E64" s="10">
-        <v>0</v>
-      </c>
-      <c r="F64" s="11" t="s">
+      <c r="D64" s="11">
+        <v>60</v>
+      </c>
+      <c r="E64" s="11">
+        <v>0</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G64" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H64" s="8">
+      <c r="G64" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H64" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:8">
-      <c r="A65" s="8">
+      <c r="A65" s="9">
         <v>103800104</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="10">
         <v>250</v>
       </c>
-      <c r="D65" s="10">
-        <v>300</v>
-      </c>
-      <c r="E65" s="10">
-        <v>0</v>
-      </c>
-      <c r="F65" s="11" t="s">
+      <c r="D65" s="11">
+        <v>300</v>
+      </c>
+      <c r="E65" s="11">
+        <v>0</v>
+      </c>
+      <c r="F65" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G65" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H65" s="8">
+      <c r="G65" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H65" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:8">
-      <c r="A66" s="8">
+      <c r="A66" s="9">
         <v>102700101</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="10">
         <v>10</v>
       </c>
-      <c r="D66" s="10">
-        <v>15</v>
-      </c>
-      <c r="E66" s="10">
-        <v>0</v>
-      </c>
-      <c r="F66" s="11" t="s">
+      <c r="D66" s="11">
+        <v>15</v>
+      </c>
+      <c r="E66" s="11">
+        <v>0</v>
+      </c>
+      <c r="F66" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G66" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H66" s="8">
+      <c r="G66" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H66" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:8">
-      <c r="A67" s="8">
+      <c r="A67" s="9">
         <v>102700102</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="9">
-        <v>20</v>
-      </c>
-      <c r="D67" s="10">
-        <v>25</v>
-      </c>
-      <c r="E67" s="10">
-        <v>0</v>
-      </c>
-      <c r="F67" s="11" t="s">
+      <c r="C67" s="10">
+        <v>20</v>
+      </c>
+      <c r="D67" s="11">
+        <v>25</v>
+      </c>
+      <c r="E67" s="11">
+        <v>0</v>
+      </c>
+      <c r="F67" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G67" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H67" s="8">
+      <c r="G67" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H67" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:8">
-      <c r="A68" s="8">
+      <c r="A68" s="9">
         <v>102700103</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="9">
+      <c r="B68" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="10">
         <v>50</v>
       </c>
-      <c r="D68" s="10">
-        <v>60</v>
-      </c>
-      <c r="E68" s="10">
-        <v>0</v>
-      </c>
-      <c r="F68" s="11" t="s">
+      <c r="D68" s="11">
+        <v>60</v>
+      </c>
+      <c r="E68" s="11">
+        <v>0</v>
+      </c>
+      <c r="F68" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G68" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H68" s="8">
+      <c r="G68" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H68" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:8">
-      <c r="A69" s="8">
+      <c r="A69" s="9">
         <v>102700104</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="10">
         <v>250</v>
       </c>
-      <c r="D69" s="10">
-        <v>300</v>
-      </c>
-      <c r="E69" s="10">
-        <v>0</v>
-      </c>
-      <c r="F69" s="11" t="s">
+      <c r="D69" s="11">
+        <v>300</v>
+      </c>
+      <c r="E69" s="11">
+        <v>0</v>
+      </c>
+      <c r="F69" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G69" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H69" s="8">
+      <c r="G69" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H69" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:8">
-      <c r="A70" s="8">
+      <c r="A70" s="9">
         <v>103700101</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C70" s="9">
-        <v>0</v>
-      </c>
-      <c r="D70" s="10">
-        <v>0</v>
-      </c>
-      <c r="E70" s="10">
+      <c r="C70" s="10">
+        <v>0</v>
+      </c>
+      <c r="D70" s="11">
+        <v>0</v>
+      </c>
+      <c r="E70" s="11">
         <v>1000</v>
       </c>
-      <c r="F70" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" s="8">
-        <v>0</v>
-      </c>
-      <c r="H70" s="8">
+      <c r="F70" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:8">
-      <c r="A71" s="8">
+      <c r="A71" s="9">
         <v>103100101</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71" s="10">
         <v>10</v>
       </c>
-      <c r="D71" s="10">
-        <v>15</v>
-      </c>
-      <c r="E71" s="10">
-        <v>0</v>
-      </c>
-      <c r="F71" s="11" t="s">
+      <c r="D71" s="11">
+        <v>15</v>
+      </c>
+      <c r="E71" s="11">
+        <v>0</v>
+      </c>
+      <c r="F71" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G71" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H71" s="8">
+      <c r="G71" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H71" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:8">
-      <c r="A72" s="8">
+      <c r="A72" s="9">
         <v>103100102</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C72" s="9">
-        <v>20</v>
-      </c>
-      <c r="D72" s="10">
-        <v>25</v>
-      </c>
-      <c r="E72" s="10">
-        <v>0</v>
-      </c>
-      <c r="F72" s="11" t="s">
+      <c r="C72" s="10">
+        <v>20</v>
+      </c>
+      <c r="D72" s="11">
+        <v>25</v>
+      </c>
+      <c r="E72" s="11">
+        <v>0</v>
+      </c>
+      <c r="F72" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G72" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H72" s="8">
+      <c r="G72" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H72" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:8">
-      <c r="A73" s="8">
+      <c r="A73" s="9">
         <v>103100103</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="9">
+      <c r="B73" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="10">
         <v>50</v>
       </c>
-      <c r="D73" s="10">
-        <v>60</v>
-      </c>
-      <c r="E73" s="10">
-        <v>0</v>
-      </c>
-      <c r="F73" s="11" t="s">
+      <c r="D73" s="11">
+        <v>60</v>
+      </c>
+      <c r="E73" s="11">
+        <v>0</v>
+      </c>
+      <c r="F73" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G73" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H73" s="8">
+      <c r="G73" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H73" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:8">
-      <c r="A74" s="8">
+      <c r="A74" s="9">
         <v>103100104</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="10">
         <v>250</v>
       </c>
-      <c r="D74" s="10">
-        <v>300</v>
-      </c>
-      <c r="E74" s="10">
-        <v>0</v>
-      </c>
-      <c r="F74" s="11" t="s">
+      <c r="D74" s="11">
+        <v>300</v>
+      </c>
+      <c r="E74" s="11">
+        <v>0</v>
+      </c>
+      <c r="F74" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G74" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H74" s="8">
+      <c r="G74" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H74" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:8">
-      <c r="A75" s="8">
+      <c r="A75" s="9">
         <v>104000101</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75" s="10">
         <v>10</v>
       </c>
-      <c r="D75" s="10">
-        <v>15</v>
-      </c>
-      <c r="E75" s="10">
-        <v>0</v>
-      </c>
-      <c r="F75" s="11" t="s">
+      <c r="D75" s="11">
+        <v>15</v>
+      </c>
+      <c r="E75" s="11">
+        <v>0</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G75" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H75" s="8">
+      <c r="G75" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H75" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:8">
-      <c r="A76" s="8">
+      <c r="A76" s="9">
         <v>104000102</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="9">
-        <v>20</v>
-      </c>
-      <c r="D76" s="10">
-        <v>25</v>
-      </c>
-      <c r="E76" s="10">
-        <v>0</v>
-      </c>
-      <c r="F76" s="11" t="s">
+      <c r="C76" s="10">
+        <v>20</v>
+      </c>
+      <c r="D76" s="11">
+        <v>25</v>
+      </c>
+      <c r="E76" s="11">
+        <v>0</v>
+      </c>
+      <c r="F76" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G76" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H76" s="8">
+      <c r="G76" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H76" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:8">
-      <c r="A77" s="8">
+      <c r="A77" s="9">
         <v>104000103</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77" s="9">
+      <c r="B77" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="10">
         <v>50</v>
       </c>
-      <c r="D77" s="10">
-        <v>60</v>
-      </c>
-      <c r="E77" s="10">
-        <v>0</v>
-      </c>
-      <c r="F77" s="11" t="s">
+      <c r="D77" s="11">
+        <v>60</v>
+      </c>
+      <c r="E77" s="11">
+        <v>0</v>
+      </c>
+      <c r="F77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G77" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H77" s="8">
+      <c r="G77" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H77" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:8">
-      <c r="A78" s="8">
+      <c r="A78" s="9">
         <v>104000104</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="10">
         <v>250</v>
       </c>
-      <c r="D78" s="10">
-        <v>300</v>
-      </c>
-      <c r="E78" s="10">
-        <v>0</v>
-      </c>
-      <c r="F78" s="11" t="s">
+      <c r="D78" s="11">
+        <v>300</v>
+      </c>
+      <c r="E78" s="11">
+        <v>0</v>
+      </c>
+      <c r="F78" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G78" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H78" s="8">
+      <c r="G78" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H78" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:8">
-      <c r="A79" s="8">
+      <c r="A79" s="9">
         <v>103900101</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="10">
         <v>10</v>
       </c>
-      <c r="D79" s="10">
-        <v>15</v>
-      </c>
-      <c r="E79" s="10">
-        <v>0</v>
-      </c>
-      <c r="F79" s="11" t="s">
+      <c r="D79" s="11">
+        <v>15</v>
+      </c>
+      <c r="E79" s="11">
+        <v>0</v>
+      </c>
+      <c r="F79" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G79" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H79" s="8">
+      <c r="G79" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H79" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:8">
-      <c r="A80" s="8">
+      <c r="A80" s="9">
         <v>103900102</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="9">
-        <v>20</v>
-      </c>
-      <c r="D80" s="10">
-        <v>25</v>
-      </c>
-      <c r="E80" s="10">
-        <v>0</v>
-      </c>
-      <c r="F80" s="11" t="s">
+      <c r="C80" s="10">
+        <v>20</v>
+      </c>
+      <c r="D80" s="11">
+        <v>25</v>
+      </c>
+      <c r="E80" s="11">
+        <v>0</v>
+      </c>
+      <c r="F80" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G80" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H80" s="8">
+      <c r="G80" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H80" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:9">
-      <c r="A81" s="8">
+      <c r="A81" s="9">
         <v>103900103</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="9">
+      <c r="B81" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="10">
         <v>50</v>
       </c>
-      <c r="D81" s="10">
-        <v>60</v>
-      </c>
-      <c r="E81" s="10">
-        <v>0</v>
-      </c>
-      <c r="F81" s="11" t="s">
+      <c r="D81" s="11">
+        <v>60</v>
+      </c>
+      <c r="E81" s="11">
+        <v>0</v>
+      </c>
+      <c r="F81" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G81" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H81" s="8">
+      <c r="G81" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H81" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:9">
-      <c r="A82" s="8">
+      <c r="A82" s="9">
         <v>103900104</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="10">
         <v>250</v>
       </c>
-      <c r="D82" s="10">
-        <v>300</v>
-      </c>
-      <c r="E82" s="10">
-        <v>0</v>
-      </c>
-      <c r="F82" s="11" t="s">
+      <c r="D82" s="11">
+        <v>300</v>
+      </c>
+      <c r="E82" s="11">
+        <v>0</v>
+      </c>
+      <c r="F82" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G82" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H82" s="8">
+      <c r="G82" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H82" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:9">
-      <c r="A83" s="8">
+      <c r="A83" s="9">
         <v>101600101</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="10">
         <v>10</v>
       </c>
-      <c r="D83" s="10">
-        <v>15</v>
-      </c>
-      <c r="E83" s="10">
-        <v>0</v>
-      </c>
-      <c r="F83" s="11" t="s">
+      <c r="D83" s="11">
+        <v>15</v>
+      </c>
+      <c r="E83" s="11">
+        <v>0</v>
+      </c>
+      <c r="F83" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G83" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H83" s="8">
+      <c r="G83" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H83" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:9">
-      <c r="A84" s="8">
+      <c r="A84" s="9">
         <v>101600102</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C84" s="9">
-        <v>20</v>
-      </c>
-      <c r="D84" s="10">
-        <v>25</v>
-      </c>
-      <c r="E84" s="10">
-        <v>0</v>
-      </c>
-      <c r="F84" s="11" t="s">
+      <c r="C84" s="10">
+        <v>20</v>
+      </c>
+      <c r="D84" s="11">
+        <v>25</v>
+      </c>
+      <c r="E84" s="11">
+        <v>0</v>
+      </c>
+      <c r="F84" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G84" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H84" s="8">
+      <c r="G84" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H84" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:9">
-      <c r="A85" s="8">
+      <c r="A85" s="9">
         <v>101600103</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85" s="9">
+      <c r="B85" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" s="10">
         <v>50</v>
       </c>
-      <c r="D85" s="10">
-        <v>60</v>
-      </c>
-      <c r="E85" s="10">
-        <v>0</v>
-      </c>
-      <c r="F85" s="11" t="s">
+      <c r="D85" s="11">
+        <v>60</v>
+      </c>
+      <c r="E85" s="11">
+        <v>0</v>
+      </c>
+      <c r="F85" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G85" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H85" s="8">
+      <c r="G85" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H85" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:9">
-      <c r="A86" s="8">
+      <c r="A86" s="9">
         <v>101600104</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="10">
         <v>250</v>
       </c>
-      <c r="D86" s="10">
-        <v>300</v>
-      </c>
-      <c r="E86" s="10">
-        <v>0</v>
-      </c>
-      <c r="F86" s="11" t="s">
+      <c r="D86" s="11">
+        <v>300</v>
+      </c>
+      <c r="E86" s="11">
+        <v>0</v>
+      </c>
+      <c r="F86" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G86" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H86" s="8">
+      <c r="G86" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H86" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:9">
-      <c r="A87" s="8">
+      <c r="A87" s="9">
         <v>101500101</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C87" s="10">
         <v>10</v>
       </c>
-      <c r="D87" s="10">
-        <v>15</v>
-      </c>
-      <c r="E87" s="10">
-        <v>0</v>
-      </c>
-      <c r="F87" s="11" t="s">
+      <c r="D87" s="11">
+        <v>15</v>
+      </c>
+      <c r="E87" s="11">
+        <v>0</v>
+      </c>
+      <c r="F87" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G87" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H87" s="8">
+      <c r="G87" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H87" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:9">
-      <c r="A88" s="8">
+      <c r="A88" s="9">
         <v>101500102</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C88" s="9">
-        <v>20</v>
-      </c>
-      <c r="D88" s="10">
-        <v>25</v>
-      </c>
-      <c r="E88" s="10">
-        <v>0</v>
-      </c>
-      <c r="F88" s="11" t="s">
+      <c r="C88" s="10">
+        <v>20</v>
+      </c>
+      <c r="D88" s="11">
+        <v>25</v>
+      </c>
+      <c r="E88" s="11">
+        <v>0</v>
+      </c>
+      <c r="F88" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H88" s="8">
+      <c r="G88" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H88" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:9">
-      <c r="A89" s="8">
+      <c r="A89" s="9">
         <v>101500103</v>
       </c>
-      <c r="B89" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C89" s="9">
+      <c r="B89" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="10">
         <v>50</v>
       </c>
-      <c r="D89" s="10">
-        <v>60</v>
-      </c>
-      <c r="E89" s="10">
-        <v>0</v>
-      </c>
-      <c r="F89" s="11" t="s">
+      <c r="D89" s="11">
+        <v>60</v>
+      </c>
+      <c r="E89" s="11">
+        <v>0</v>
+      </c>
+      <c r="F89" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G89" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H89" s="8">
+      <c r="G89" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H89" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:9">
-      <c r="A90" s="8">
+      <c r="A90" s="9">
         <v>101500104</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="10">
         <v>250</v>
       </c>
-      <c r="D90" s="10">
-        <v>300</v>
-      </c>
-      <c r="E90" s="10">
-        <v>0</v>
-      </c>
-      <c r="F90" s="11" t="s">
+      <c r="D90" s="11">
+        <v>300</v>
+      </c>
+      <c r="E90" s="11">
+        <v>0</v>
+      </c>
+      <c r="F90" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G90" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H90" s="8">
+      <c r="G90" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H90" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:9">
-      <c r="A91" s="8">
+      <c r="A91" s="9">
         <v>102600101</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91" s="10">
         <v>10</v>
       </c>
-      <c r="D91" s="10">
-        <v>15</v>
-      </c>
-      <c r="E91" s="10">
-        <v>0</v>
-      </c>
-      <c r="F91" s="11" t="s">
+      <c r="D91" s="11">
+        <v>15</v>
+      </c>
+      <c r="E91" s="11">
+        <v>0</v>
+      </c>
+      <c r="F91" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G91" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H91" s="8">
+      <c r="G91" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H91" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:9">
-      <c r="A92" s="8">
+      <c r="A92" s="9">
         <v>102600102</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C92" s="9">
-        <v>20</v>
-      </c>
-      <c r="D92" s="10">
-        <v>25</v>
-      </c>
-      <c r="E92" s="10">
-        <v>0</v>
-      </c>
-      <c r="F92" s="11" t="s">
+      <c r="C92" s="10">
+        <v>20</v>
+      </c>
+      <c r="D92" s="11">
+        <v>25</v>
+      </c>
+      <c r="E92" s="11">
+        <v>0</v>
+      </c>
+      <c r="F92" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G92" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H92" s="8">
+      <c r="G92" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H92" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:9">
-      <c r="A93" s="8">
+      <c r="A93" s="9">
         <v>102600103</v>
       </c>
-      <c r="B93" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C93" s="9">
+      <c r="B93" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="10">
         <v>50</v>
       </c>
-      <c r="D93" s="10">
-        <v>60</v>
-      </c>
-      <c r="E93" s="10">
-        <v>0</v>
-      </c>
-      <c r="F93" s="11" t="s">
+      <c r="D93" s="11">
+        <v>60</v>
+      </c>
+      <c r="E93" s="11">
+        <v>0</v>
+      </c>
+      <c r="F93" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G93" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H93" s="8">
+      <c r="G93" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H93" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:9">
-      <c r="A94" s="8">
+      <c r="A94" s="9">
         <v>102600104</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="10">
         <v>250</v>
       </c>
-      <c r="D94" s="10">
-        <v>300</v>
-      </c>
-      <c r="E94" s="10">
-        <v>0</v>
-      </c>
-      <c r="F94" s="11" t="s">
+      <c r="D94" s="11">
+        <v>300</v>
+      </c>
+      <c r="E94" s="11">
+        <v>0</v>
+      </c>
+      <c r="F94" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G94" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H94" s="8">
+      <c r="G94" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H94" s="9">
         <v>300</v>
       </c>
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A95" s="8">
+      <c r="A95" s="9">
         <v>105000101</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="10">
         <v>10</v>
       </c>
-      <c r="D95" s="10">
-        <v>15</v>
-      </c>
-      <c r="E95" s="10">
-        <v>0</v>
-      </c>
-      <c r="F95" s="11" t="s">
+      <c r="D95" s="11">
+        <v>15</v>
+      </c>
+      <c r="E95" s="11">
+        <v>0</v>
+      </c>
+      <c r="F95" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G95" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H95" s="8">
-        <v>15</v>
-      </c>
-      <c r="I95" s="2"/>
+      <c r="G95" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H95" s="9">
+        <v>15</v>
+      </c>
+      <c r="I95" s="3"/>
     </row>
     <row r="96" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A96" s="8">
+      <c r="A96" s="9">
         <v>105000102</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="9">
-        <v>20</v>
-      </c>
-      <c r="D96" s="10">
-        <v>25</v>
-      </c>
-      <c r="E96" s="10">
-        <v>0</v>
-      </c>
-      <c r="F96" s="11" t="s">
+      <c r="C96" s="10">
+        <v>20</v>
+      </c>
+      <c r="D96" s="11">
+        <v>25</v>
+      </c>
+      <c r="E96" s="11">
+        <v>0</v>
+      </c>
+      <c r="F96" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G96" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H96" s="8">
-        <v>25</v>
-      </c>
-      <c r="I96" s="2"/>
+      <c r="G96" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H96" s="9">
+        <v>25</v>
+      </c>
+      <c r="I96" s="3"/>
     </row>
     <row r="97" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A97" s="8">
+      <c r="A97" s="9">
         <v>105000103</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C97" s="9">
+      <c r="B97" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="10">
         <v>50</v>
       </c>
-      <c r="D97" s="10">
-        <v>60</v>
-      </c>
-      <c r="E97" s="10">
-        <v>0</v>
-      </c>
-      <c r="F97" s="11" t="s">
+      <c r="D97" s="11">
+        <v>60</v>
+      </c>
+      <c r="E97" s="11">
+        <v>0</v>
+      </c>
+      <c r="F97" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G97" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H97" s="8">
-        <v>60</v>
-      </c>
-      <c r="I97" s="2"/>
+      <c r="G97" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H97" s="9">
+        <v>60</v>
+      </c>
+      <c r="I97" s="3"/>
     </row>
     <row r="98" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A98" s="8">
+      <c r="A98" s="9">
         <v>105000104</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="10">
         <v>250</v>
       </c>
-      <c r="D98" s="10">
-        <v>300</v>
-      </c>
-      <c r="E98" s="10">
-        <v>0</v>
-      </c>
-      <c r="F98" s="11" t="s">
+      <c r="D98" s="11">
+        <v>300</v>
+      </c>
+      <c r="E98" s="11">
+        <v>0</v>
+      </c>
+      <c r="F98" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G98" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H98" s="8">
-        <v>300</v>
-      </c>
-      <c r="I98" s="2"/>
+      <c r="G98" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H98" s="9">
+        <v>300</v>
+      </c>
+      <c r="I98" s="3"/>
     </row>
     <row r="99" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A99" s="8">
+      <c r="A99" s="9">
         <v>105100101</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="10">
         <v>10</v>
       </c>
-      <c r="D99" s="10">
-        <v>15</v>
-      </c>
-      <c r="E99" s="10">
-        <v>0</v>
-      </c>
-      <c r="F99" s="11" t="s">
+      <c r="D99" s="11">
+        <v>15</v>
+      </c>
+      <c r="E99" s="11">
+        <v>0</v>
+      </c>
+      <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H99" s="8">
-        <v>15</v>
-      </c>
-      <c r="I99" s="2"/>
+      <c r="G99" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H99" s="9">
+        <v>15</v>
+      </c>
+      <c r="I99" s="3"/>
     </row>
     <row r="100" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A100" s="8">
+      <c r="A100" s="9">
         <v>105100102</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C100" s="9">
-        <v>20</v>
-      </c>
-      <c r="D100" s="10">
-        <v>25</v>
-      </c>
-      <c r="E100" s="10">
-        <v>0</v>
-      </c>
-      <c r="F100" s="11" t="s">
+      <c r="C100" s="10">
+        <v>20</v>
+      </c>
+      <c r="D100" s="11">
+        <v>25</v>
+      </c>
+      <c r="E100" s="11">
+        <v>0</v>
+      </c>
+      <c r="F100" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G100" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H100" s="8">
-        <v>25</v>
-      </c>
-      <c r="I100" s="2"/>
+      <c r="G100" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H100" s="9">
+        <v>25</v>
+      </c>
+      <c r="I100" s="3"/>
     </row>
     <row r="101" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A101" s="8">
+      <c r="A101" s="9">
         <v>105100103</v>
       </c>
-      <c r="B101" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C101" s="9">
+      <c r="B101" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="10">
         <v>50</v>
       </c>
-      <c r="D101" s="10">
-        <v>60</v>
-      </c>
-      <c r="E101" s="10">
-        <v>0</v>
-      </c>
-      <c r="F101" s="11" t="s">
+      <c r="D101" s="11">
+        <v>60</v>
+      </c>
+      <c r="E101" s="11">
+        <v>0</v>
+      </c>
+      <c r="F101" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G101" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H101" s="8">
-        <v>60</v>
-      </c>
-      <c r="I101" s="2"/>
+      <c r="G101" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H101" s="9">
+        <v>60</v>
+      </c>
+      <c r="I101" s="3"/>
     </row>
     <row r="102" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A102" s="8">
+      <c r="A102" s="9">
         <v>105100104</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="10">
         <v>250</v>
       </c>
-      <c r="D102" s="10">
-        <v>300</v>
-      </c>
-      <c r="E102" s="10">
-        <v>0</v>
-      </c>
-      <c r="F102" s="11" t="s">
+      <c r="D102" s="11">
+        <v>300</v>
+      </c>
+      <c r="E102" s="11">
+        <v>0</v>
+      </c>
+      <c r="F102" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G102" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H102" s="8">
-        <v>300</v>
-      </c>
-      <c r="I102" s="2"/>
+      <c r="G102" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H102" s="9">
+        <v>300</v>
+      </c>
+      <c r="I102" s="3"/>
+    </row>
+    <row r="103" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A103" s="9">
+        <v>105400101</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" s="10">
+        <v>10</v>
+      </c>
+      <c r="D103" s="11">
+        <v>15</v>
+      </c>
+      <c r="E103" s="11">
+        <v>0</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H103" s="9">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A104" s="9">
+        <v>105400102</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" s="10">
+        <v>20</v>
+      </c>
+      <c r="D104" s="11">
+        <v>25</v>
+      </c>
+      <c r="E104" s="11">
+        <v>0</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H104" s="9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A105" s="9">
+        <v>105400103</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="10">
+        <v>50</v>
+      </c>
+      <c r="D105" s="11">
+        <v>60</v>
+      </c>
+      <c r="E105" s="11">
+        <v>0</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G105" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H105" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A106" s="9">
+        <v>105400104</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" s="10">
+        <v>250</v>
+      </c>
+      <c r="D106" s="11">
+        <v>300</v>
+      </c>
+      <c r="E106" s="11">
+        <v>0</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H106" s="9">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A107" s="9">
+        <v>100800101</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" s="10">
+        <v>10</v>
+      </c>
+      <c r="D107" s="11">
+        <v>15</v>
+      </c>
+      <c r="E107" s="11">
+        <v>0</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H107" s="9">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A108" s="9">
+        <v>100800102</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="10">
+        <v>20</v>
+      </c>
+      <c r="D108" s="11">
+        <v>25</v>
+      </c>
+      <c r="E108" s="11">
+        <v>0</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G108" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H108" s="9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A109" s="19">
+        <v>100800103</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="10">
+        <v>50</v>
+      </c>
+      <c r="D109" s="11">
+        <v>60</v>
+      </c>
+      <c r="E109" s="11">
+        <v>0</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G109" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H109" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A110" s="19">
+        <v>100800104</v>
+      </c>
+      <c r="B110" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C110" s="10">
+        <v>250</v>
+      </c>
+      <c r="D110" s="11">
+        <v>300</v>
+      </c>
+      <c r="E110" s="11">
+        <v>0</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G110" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H110" s="9">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A111" s="19">
+        <v>105700101</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" s="10">
+        <v>10</v>
+      </c>
+      <c r="D111" s="11">
+        <v>15</v>
+      </c>
+      <c r="E111" s="11">
+        <v>0</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G111" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H111" s="9">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="112" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A112" s="19">
+        <v>105700102</v>
+      </c>
+      <c r="B112" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" s="10">
+        <v>20</v>
+      </c>
+      <c r="D112" s="11">
+        <v>25</v>
+      </c>
+      <c r="E112" s="11">
+        <v>0</v>
+      </c>
+      <c r="F112" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G112" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H112" s="9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A113" s="19">
+        <v>105700103</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" s="10">
+        <v>50</v>
+      </c>
+      <c r="D113" s="11">
+        <v>60</v>
+      </c>
+      <c r="E113" s="11">
+        <v>0</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G113" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H113" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="114" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A114" s="19">
+        <v>105700104</v>
+      </c>
+      <c r="B114" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C114" s="10">
+        <v>250</v>
+      </c>
+      <c r="D114" s="11">
+        <v>300</v>
+      </c>
+      <c r="E114" s="11">
+        <v>0</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G114" s="9">
+        <v>1700</v>
+      </c>
+      <c r="H114" s="9">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A115" s="19">
+        <v>105800101</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" s="10">
+        <v>0</v>
+      </c>
+      <c r="D115" s="11">
+        <v>0</v>
+      </c>
+      <c r="E115" s="11">
+        <v>5000</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G115" s="9">
+        <v>0</v>
+      </c>
+      <c r="H115" s="9">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
